--- a/docs/【Creepy Code】ガントチャート_PC.xlsx
+++ b/docs/【Creepy Code】ガントチャート_PC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nishi\OneDrive\ドキュメント\Creepy-Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97C2C97-A9EE-4B96-902D-1EAFF6859A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60853B5F-1F0F-4941-BC9F-0DA850912C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -436,13 +436,6 @@
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>屋部憲成</t>
-    <rPh sb="2" eb="4">
-      <t>ノリナリ</t>
-    </rPh>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
     <t>画面設計</t>
     <rPh sb="0" eb="2">
       <t>ガメン</t>
@@ -507,6 +500,10 @@
       </rPr>
       <t>結合テスト</t>
     </r>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>洋介・志恩</t>
     <phoneticPr fontId="11"/>
   </si>
 </sst>
@@ -1019,6 +1016,8 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1027,8 +1026,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1378,297 +1375,297 @@
       <c r="AF1" s="5"/>
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
-      <c r="AI1" s="79" t="s">
+      <c r="AI1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" s="77"/>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="77"/>
-      <c r="AO1" s="77"/>
-      <c r="AP1" s="77"/>
-      <c r="AQ1" s="77"/>
-      <c r="AR1" s="77"/>
-      <c r="AS1" s="77"/>
-      <c r="AT1" s="77"/>
-      <c r="AU1" s="77"/>
-      <c r="AV1" s="77"/>
-      <c r="AW1" s="77"/>
-      <c r="AX1" s="77"/>
-      <c r="AY1" s="77"/>
-      <c r="AZ1" s="77"/>
-      <c r="BA1" s="77"/>
-      <c r="BB1" s="77"/>
-      <c r="BC1" s="77"/>
-      <c r="BD1" s="77"/>
-      <c r="BE1" s="77"/>
-      <c r="BF1" s="77"/>
-      <c r="BG1" s="77"/>
-      <c r="BH1" s="77"/>
-      <c r="BI1" s="77"/>
-      <c r="BJ1" s="77"/>
-      <c r="BK1" s="77"/>
-      <c r="BL1" s="78"/>
-      <c r="BM1" s="76" t="s">
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+      <c r="BC1" s="79"/>
+      <c r="BD1" s="79"/>
+      <c r="BE1" s="79"/>
+      <c r="BF1" s="79"/>
+      <c r="BG1" s="79"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
+      <c r="BJ1" s="79"/>
+      <c r="BK1" s="79"/>
+      <c r="BL1" s="80"/>
+      <c r="BM1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="BN1" s="77"/>
-      <c r="BO1" s="77"/>
-      <c r="BP1" s="77"/>
-      <c r="BQ1" s="77"/>
-      <c r="BR1" s="77"/>
-      <c r="BS1" s="77"/>
-      <c r="BT1" s="77"/>
-      <c r="BU1" s="77"/>
-      <c r="BV1" s="77"/>
-      <c r="BW1" s="77"/>
-      <c r="BX1" s="77"/>
-      <c r="BY1" s="77"/>
-      <c r="BZ1" s="77"/>
-      <c r="CA1" s="77"/>
-      <c r="CB1" s="77"/>
-      <c r="CC1" s="77"/>
-      <c r="CD1" s="77"/>
-      <c r="CE1" s="77"/>
-      <c r="CF1" s="77"/>
-      <c r="CG1" s="77"/>
-      <c r="CH1" s="77"/>
-      <c r="CI1" s="77"/>
-      <c r="CJ1" s="77"/>
-      <c r="CK1" s="77"/>
-      <c r="CL1" s="77"/>
-      <c r="CM1" s="77"/>
-      <c r="CN1" s="77"/>
-      <c r="CO1" s="77"/>
-      <c r="CP1" s="77"/>
-      <c r="CQ1" s="78"/>
-      <c r="CR1" s="76" t="s">
+      <c r="BN1" s="79"/>
+      <c r="BO1" s="79"/>
+      <c r="BP1" s="79"/>
+      <c r="BQ1" s="79"/>
+      <c r="BR1" s="79"/>
+      <c r="BS1" s="79"/>
+      <c r="BT1" s="79"/>
+      <c r="BU1" s="79"/>
+      <c r="BV1" s="79"/>
+      <c r="BW1" s="79"/>
+      <c r="BX1" s="79"/>
+      <c r="BY1" s="79"/>
+      <c r="BZ1" s="79"/>
+      <c r="CA1" s="79"/>
+      <c r="CB1" s="79"/>
+      <c r="CC1" s="79"/>
+      <c r="CD1" s="79"/>
+      <c r="CE1" s="79"/>
+      <c r="CF1" s="79"/>
+      <c r="CG1" s="79"/>
+      <c r="CH1" s="79"/>
+      <c r="CI1" s="79"/>
+      <c r="CJ1" s="79"/>
+      <c r="CK1" s="79"/>
+      <c r="CL1" s="79"/>
+      <c r="CM1" s="79"/>
+      <c r="CN1" s="79"/>
+      <c r="CO1" s="79"/>
+      <c r="CP1" s="79"/>
+      <c r="CQ1" s="80"/>
+      <c r="CR1" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="CS1" s="77"/>
-      <c r="CT1" s="77"/>
-      <c r="CU1" s="77"/>
-      <c r="CV1" s="77"/>
-      <c r="CW1" s="77"/>
-      <c r="CX1" s="77"/>
-      <c r="CY1" s="77"/>
-      <c r="CZ1" s="77"/>
-      <c r="DA1" s="77"/>
-      <c r="DB1" s="77"/>
-      <c r="DC1" s="77"/>
-      <c r="DD1" s="77"/>
-      <c r="DE1" s="77"/>
-      <c r="DF1" s="77"/>
-      <c r="DG1" s="77"/>
-      <c r="DH1" s="77"/>
-      <c r="DI1" s="77"/>
-      <c r="DJ1" s="77"/>
-      <c r="DK1" s="77"/>
-      <c r="DL1" s="77"/>
-      <c r="DM1" s="77"/>
-      <c r="DN1" s="77"/>
-      <c r="DO1" s="77"/>
-      <c r="DP1" s="77"/>
-      <c r="DQ1" s="77"/>
-      <c r="DR1" s="77"/>
-      <c r="DS1" s="77"/>
-      <c r="DT1" s="77"/>
-      <c r="DU1" s="77"/>
-      <c r="DV1" s="78"/>
-      <c r="DW1" s="76" t="s">
+      <c r="CS1" s="79"/>
+      <c r="CT1" s="79"/>
+      <c r="CU1" s="79"/>
+      <c r="CV1" s="79"/>
+      <c r="CW1" s="79"/>
+      <c r="CX1" s="79"/>
+      <c r="CY1" s="79"/>
+      <c r="CZ1" s="79"/>
+      <c r="DA1" s="79"/>
+      <c r="DB1" s="79"/>
+      <c r="DC1" s="79"/>
+      <c r="DD1" s="79"/>
+      <c r="DE1" s="79"/>
+      <c r="DF1" s="79"/>
+      <c r="DG1" s="79"/>
+      <c r="DH1" s="79"/>
+      <c r="DI1" s="79"/>
+      <c r="DJ1" s="79"/>
+      <c r="DK1" s="79"/>
+      <c r="DL1" s="79"/>
+      <c r="DM1" s="79"/>
+      <c r="DN1" s="79"/>
+      <c r="DO1" s="79"/>
+      <c r="DP1" s="79"/>
+      <c r="DQ1" s="79"/>
+      <c r="DR1" s="79"/>
+      <c r="DS1" s="79"/>
+      <c r="DT1" s="79"/>
+      <c r="DU1" s="79"/>
+      <c r="DV1" s="80"/>
+      <c r="DW1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="DX1" s="77"/>
-      <c r="DY1" s="77"/>
-      <c r="DZ1" s="77"/>
-      <c r="EA1" s="77"/>
-      <c r="EB1" s="77"/>
-      <c r="EC1" s="77"/>
-      <c r="ED1" s="77"/>
-      <c r="EE1" s="77"/>
-      <c r="EF1" s="77"/>
-      <c r="EG1" s="77"/>
-      <c r="EH1" s="77"/>
-      <c r="EI1" s="77"/>
-      <c r="EJ1" s="77"/>
-      <c r="EK1" s="77"/>
-      <c r="EL1" s="77"/>
-      <c r="EM1" s="77"/>
-      <c r="EN1" s="77"/>
-      <c r="EO1" s="77"/>
-      <c r="EP1" s="77"/>
-      <c r="EQ1" s="77"/>
-      <c r="ER1" s="77"/>
-      <c r="ES1" s="77"/>
-      <c r="ET1" s="77"/>
-      <c r="EU1" s="77"/>
-      <c r="EV1" s="77"/>
-      <c r="EW1" s="77"/>
-      <c r="EX1" s="77"/>
-      <c r="EY1" s="77"/>
-      <c r="EZ1" s="77"/>
-      <c r="FA1" s="76" t="s">
+      <c r="DX1" s="79"/>
+      <c r="DY1" s="79"/>
+      <c r="DZ1" s="79"/>
+      <c r="EA1" s="79"/>
+      <c r="EB1" s="79"/>
+      <c r="EC1" s="79"/>
+      <c r="ED1" s="79"/>
+      <c r="EE1" s="79"/>
+      <c r="EF1" s="79"/>
+      <c r="EG1" s="79"/>
+      <c r="EH1" s="79"/>
+      <c r="EI1" s="79"/>
+      <c r="EJ1" s="79"/>
+      <c r="EK1" s="79"/>
+      <c r="EL1" s="79"/>
+      <c r="EM1" s="79"/>
+      <c r="EN1" s="79"/>
+      <c r="EO1" s="79"/>
+      <c r="EP1" s="79"/>
+      <c r="EQ1" s="79"/>
+      <c r="ER1" s="79"/>
+      <c r="ES1" s="79"/>
+      <c r="ET1" s="79"/>
+      <c r="EU1" s="79"/>
+      <c r="EV1" s="79"/>
+      <c r="EW1" s="79"/>
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="FB1" s="77"/>
-      <c r="FC1" s="77"/>
-      <c r="FD1" s="77"/>
-      <c r="FE1" s="77"/>
-      <c r="FF1" s="77"/>
-      <c r="FG1" s="77"/>
-      <c r="FH1" s="77"/>
-      <c r="FI1" s="77"/>
-      <c r="FJ1" s="77"/>
-      <c r="FK1" s="77"/>
-      <c r="FL1" s="77"/>
-      <c r="FM1" s="77"/>
-      <c r="FN1" s="77"/>
-      <c r="FO1" s="77"/>
-      <c r="FP1" s="77"/>
-      <c r="FQ1" s="77"/>
-      <c r="FR1" s="77"/>
-      <c r="FS1" s="77"/>
-      <c r="FT1" s="77"/>
-      <c r="FU1" s="77"/>
-      <c r="FV1" s="77"/>
-      <c r="FW1" s="77"/>
-      <c r="FX1" s="77"/>
-      <c r="FY1" s="77"/>
-      <c r="FZ1" s="77"/>
-      <c r="GA1" s="77"/>
-      <c r="GB1" s="77"/>
-      <c r="GC1" s="77"/>
-      <c r="GD1" s="77"/>
-      <c r="GE1" s="78"/>
-      <c r="GF1" s="76" t="s">
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="79"/>
+      <c r="GA1" s="79"/>
+      <c r="GB1" s="79"/>
+      <c r="GC1" s="79"/>
+      <c r="GD1" s="79"/>
+      <c r="GE1" s="80"/>
+      <c r="GF1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="GG1" s="77"/>
-      <c r="GH1" s="77"/>
-      <c r="GI1" s="77"/>
-      <c r="GJ1" s="77"/>
-      <c r="GK1" s="77"/>
-      <c r="GL1" s="77"/>
-      <c r="GM1" s="77"/>
-      <c r="GN1" s="77"/>
-      <c r="GO1" s="77"/>
-      <c r="GP1" s="77"/>
-      <c r="GQ1" s="77"/>
-      <c r="GR1" s="77"/>
-      <c r="GS1" s="77"/>
-      <c r="GT1" s="77"/>
-      <c r="GU1" s="77"/>
-      <c r="GV1" s="77"/>
-      <c r="GW1" s="77"/>
-      <c r="GX1" s="77"/>
-      <c r="GY1" s="77"/>
-      <c r="GZ1" s="77"/>
-      <c r="HA1" s="77"/>
-      <c r="HB1" s="77"/>
-      <c r="HC1" s="77"/>
-      <c r="HD1" s="77"/>
-      <c r="HE1" s="77"/>
-      <c r="HF1" s="77"/>
-      <c r="HG1" s="77"/>
-      <c r="HH1" s="77"/>
-      <c r="HI1" s="77"/>
-      <c r="HJ1" s="76" t="s">
+      <c r="GG1" s="79"/>
+      <c r="GH1" s="79"/>
+      <c r="GI1" s="79"/>
+      <c r="GJ1" s="79"/>
+      <c r="GK1" s="79"/>
+      <c r="GL1" s="79"/>
+      <c r="GM1" s="79"/>
+      <c r="GN1" s="79"/>
+      <c r="GO1" s="79"/>
+      <c r="GP1" s="79"/>
+      <c r="GQ1" s="79"/>
+      <c r="GR1" s="79"/>
+      <c r="GS1" s="79"/>
+      <c r="GT1" s="79"/>
+      <c r="GU1" s="79"/>
+      <c r="GV1" s="79"/>
+      <c r="GW1" s="79"/>
+      <c r="GX1" s="79"/>
+      <c r="GY1" s="79"/>
+      <c r="GZ1" s="79"/>
+      <c r="HA1" s="79"/>
+      <c r="HB1" s="79"/>
+      <c r="HC1" s="79"/>
+      <c r="HD1" s="79"/>
+      <c r="HE1" s="79"/>
+      <c r="HF1" s="79"/>
+      <c r="HG1" s="79"/>
+      <c r="HH1" s="79"/>
+      <c r="HI1" s="79"/>
+      <c r="HJ1" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="HK1" s="77"/>
-      <c r="HL1" s="77"/>
-      <c r="HM1" s="77"/>
-      <c r="HN1" s="77"/>
-      <c r="HO1" s="77"/>
-      <c r="HP1" s="77"/>
-      <c r="HQ1" s="77"/>
-      <c r="HR1" s="77"/>
-      <c r="HS1" s="77"/>
-      <c r="HT1" s="77"/>
-      <c r="HU1" s="77"/>
-      <c r="HV1" s="77"/>
-      <c r="HW1" s="77"/>
-      <c r="HX1" s="77"/>
-      <c r="HY1" s="77"/>
-      <c r="HZ1" s="77"/>
-      <c r="IA1" s="77"/>
-      <c r="IB1" s="77"/>
-      <c r="IC1" s="77"/>
-      <c r="ID1" s="77"/>
-      <c r="IE1" s="77"/>
-      <c r="IF1" s="77"/>
-      <c r="IG1" s="77"/>
-      <c r="IH1" s="77"/>
-      <c r="II1" s="77"/>
-      <c r="IJ1" s="77"/>
-      <c r="IK1" s="77"/>
-      <c r="IL1" s="77"/>
-      <c r="IM1" s="77"/>
-      <c r="IN1" s="78"/>
-      <c r="IO1" s="76" t="s">
+      <c r="HK1" s="79"/>
+      <c r="HL1" s="79"/>
+      <c r="HM1" s="79"/>
+      <c r="HN1" s="79"/>
+      <c r="HO1" s="79"/>
+      <c r="HP1" s="79"/>
+      <c r="HQ1" s="79"/>
+      <c r="HR1" s="79"/>
+      <c r="HS1" s="79"/>
+      <c r="HT1" s="79"/>
+      <c r="HU1" s="79"/>
+      <c r="HV1" s="79"/>
+      <c r="HW1" s="79"/>
+      <c r="HX1" s="79"/>
+      <c r="HY1" s="79"/>
+      <c r="HZ1" s="79"/>
+      <c r="IA1" s="79"/>
+      <c r="IB1" s="79"/>
+      <c r="IC1" s="79"/>
+      <c r="ID1" s="79"/>
+      <c r="IE1" s="79"/>
+      <c r="IF1" s="79"/>
+      <c r="IG1" s="79"/>
+      <c r="IH1" s="79"/>
+      <c r="II1" s="79"/>
+      <c r="IJ1" s="79"/>
+      <c r="IK1" s="79"/>
+      <c r="IL1" s="79"/>
+      <c r="IM1" s="79"/>
+      <c r="IN1" s="80"/>
+      <c r="IO1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="IP1" s="77"/>
-      <c r="IQ1" s="77"/>
-      <c r="IR1" s="77"/>
-      <c r="IS1" s="77"/>
-      <c r="IT1" s="77"/>
-      <c r="IU1" s="77"/>
-      <c r="IV1" s="77"/>
-      <c r="IW1" s="77"/>
-      <c r="IX1" s="77"/>
-      <c r="IY1" s="77"/>
-      <c r="IZ1" s="77"/>
-      <c r="JA1" s="77"/>
-      <c r="JB1" s="77"/>
-      <c r="JC1" s="77"/>
-      <c r="JD1" s="77"/>
-      <c r="JE1" s="77"/>
-      <c r="JF1" s="77"/>
-      <c r="JG1" s="77"/>
-      <c r="JH1" s="77"/>
-      <c r="JI1" s="77"/>
-      <c r="JJ1" s="77"/>
-      <c r="JK1" s="77"/>
-      <c r="JL1" s="77"/>
-      <c r="JM1" s="77"/>
-      <c r="JN1" s="77"/>
-      <c r="JO1" s="77"/>
-      <c r="JP1" s="77"/>
-      <c r="JQ1" s="77"/>
-      <c r="JR1" s="77"/>
-      <c r="JS1" s="78"/>
-      <c r="JT1" s="76" t="s">
+      <c r="IP1" s="79"/>
+      <c r="IQ1" s="79"/>
+      <c r="IR1" s="79"/>
+      <c r="IS1" s="79"/>
+      <c r="IT1" s="79"/>
+      <c r="IU1" s="79"/>
+      <c r="IV1" s="79"/>
+      <c r="IW1" s="79"/>
+      <c r="IX1" s="79"/>
+      <c r="IY1" s="79"/>
+      <c r="IZ1" s="79"/>
+      <c r="JA1" s="79"/>
+      <c r="JB1" s="79"/>
+      <c r="JC1" s="79"/>
+      <c r="JD1" s="79"/>
+      <c r="JE1" s="79"/>
+      <c r="JF1" s="79"/>
+      <c r="JG1" s="79"/>
+      <c r="JH1" s="79"/>
+      <c r="JI1" s="79"/>
+      <c r="JJ1" s="79"/>
+      <c r="JK1" s="79"/>
+      <c r="JL1" s="79"/>
+      <c r="JM1" s="79"/>
+      <c r="JN1" s="79"/>
+      <c r="JO1" s="79"/>
+      <c r="JP1" s="79"/>
+      <c r="JQ1" s="79"/>
+      <c r="JR1" s="79"/>
+      <c r="JS1" s="80"/>
+      <c r="JT1" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="JU1" s="77"/>
-      <c r="JV1" s="77"/>
-      <c r="JW1" s="77"/>
-      <c r="JX1" s="77"/>
-      <c r="JY1" s="77"/>
-      <c r="JZ1" s="77"/>
-      <c r="KA1" s="77"/>
-      <c r="KB1" s="77"/>
-      <c r="KC1" s="77"/>
-      <c r="KD1" s="77"/>
-      <c r="KE1" s="77"/>
-      <c r="KF1" s="77"/>
-      <c r="KG1" s="77"/>
-      <c r="KH1" s="77"/>
-      <c r="KI1" s="77"/>
-      <c r="KJ1" s="77"/>
-      <c r="KK1" s="77"/>
-      <c r="KL1" s="77"/>
-      <c r="KM1" s="77"/>
-      <c r="KN1" s="77"/>
-      <c r="KO1" s="77"/>
-      <c r="KP1" s="77"/>
-      <c r="KQ1" s="77"/>
-      <c r="KR1" s="77"/>
-      <c r="KS1" s="77"/>
-      <c r="KT1" s="77"/>
-      <c r="KU1" s="77"/>
+      <c r="JU1" s="79"/>
+      <c r="JV1" s="79"/>
+      <c r="JW1" s="79"/>
+      <c r="JX1" s="79"/>
+      <c r="JY1" s="79"/>
+      <c r="JZ1" s="79"/>
+      <c r="KA1" s="79"/>
+      <c r="KB1" s="79"/>
+      <c r="KC1" s="79"/>
+      <c r="KD1" s="79"/>
+      <c r="KE1" s="79"/>
+      <c r="KF1" s="79"/>
+      <c r="KG1" s="79"/>
+      <c r="KH1" s="79"/>
+      <c r="KI1" s="79"/>
+      <c r="KJ1" s="79"/>
+      <c r="KK1" s="79"/>
+      <c r="KL1" s="79"/>
+      <c r="KM1" s="79"/>
+      <c r="KN1" s="79"/>
+      <c r="KO1" s="79"/>
+      <c r="KP1" s="79"/>
+      <c r="KQ1" s="79"/>
+      <c r="KR1" s="79"/>
+      <c r="KS1" s="79"/>
+      <c r="KT1" s="79"/>
+      <c r="KU1" s="79"/>
     </row>
     <row r="2" spans="1:307" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -12734,7 +12731,7 @@
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="73" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="30">
@@ -13369,8 +13366,8 @@
         <v>52</v>
       </c>
       <c r="C33" s="29"/>
-      <c r="D33" s="29" t="s">
-        <v>50</v>
+      <c r="D33" s="70" t="s">
+        <v>106</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="30">
@@ -14025,7 +14022,9 @@
       <c r="G35" s="30">
         <v>46195</v>
       </c>
-      <c r="H35" s="31"/>
+      <c r="H35" s="31">
+        <v>1</v>
+      </c>
       <c r="I35" s="29"/>
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
@@ -21540,8 +21539,8 @@
       <c r="A48" s="35">
         <v>9</v>
       </c>
-      <c r="B48" s="80" t="s">
-        <v>101</v>
+      <c r="B48" s="76" t="s">
+        <v>100</v>
       </c>
       <c r="C48" s="37"/>
       <c r="D48" s="37"/>
@@ -21853,8 +21852,8 @@
       <c r="A49" s="35">
         <v>10</v>
       </c>
-      <c r="B49" s="80" t="s">
-        <v>102</v>
+      <c r="B49" s="76" t="s">
+        <v>101</v>
       </c>
       <c r="C49" s="37"/>
       <c r="D49" s="37"/>
@@ -29465,7 +29464,7 @@
     </row>
     <row r="59" spans="1:307" ht="15.75" customHeight="1">
       <c r="A59" s="75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
@@ -31529,7 +31528,7 @@
         <v>3</v>
       </c>
       <c r="B62" s="74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C62" s="46"/>
       <c r="D62" s="46"/>
@@ -31842,7 +31841,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
@@ -32155,7 +32154,7 @@
         <v>5</v>
       </c>
       <c r="B64" s="74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
@@ -39778,8 +39777,8 @@
       <c r="A74" s="51">
         <v>3</v>
       </c>
-      <c r="B74" s="81" t="s">
-        <v>106</v>
+      <c r="B74" s="77" t="s">
+        <v>105</v>
       </c>
       <c r="C74" s="53"/>
       <c r="D74" s="53"/>

--- a/docs/【Creepy Code】ガントチャート_PC.xlsx
+++ b/docs/【Creepy Code】ガントチャート_PC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nishi\OneDrive\ドキュメント\Creepy-Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60853B5F-1F0F-4941-BC9F-0DA850912C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A4B960-BCAB-418C-809C-8CA824CB6FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="107">
   <si>
     <t>※作業予定（期間）を黄色く色づけする</t>
   </si>
@@ -198,9 +198,6 @@
     <t>セキュリティ設計</t>
   </si>
   <si>
-    <t>詳細設計書作成</t>
-  </si>
-  <si>
     <t>作業計画</t>
   </si>
   <si>
@@ -275,10 +272,6 @@
   </si>
   <si>
     <t>画面遷移図の作成</t>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>ワイヤーフレームの作成</t>
     <phoneticPr fontId="11"/>
   </si>
   <si>
@@ -506,6 +499,20 @@
     <t>洋介・志恩</t>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>アプリのテーマ決め(ロゴ・ネーム・カラー)</t>
+    <rPh sb="7" eb="8">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>詳細設計部分書作成</t>
+    <rPh sb="4" eb="6">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
@@ -516,7 +523,7 @@
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="178" formatCode="m/d"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -605,13 +612,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
@@ -891,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1013,11 +1013,10 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1030,7 +1029,18 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1375,297 +1385,297 @@
       <c r="AF1" s="5"/>
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
-      <c r="AI1" s="81" t="s">
+      <c r="AI1" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="79"/>
-      <c r="AT1" s="79"/>
-      <c r="AU1" s="79"/>
-      <c r="AV1" s="79"/>
-      <c r="AW1" s="79"/>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="79"/>
-      <c r="BC1" s="79"/>
-      <c r="BD1" s="79"/>
-      <c r="BE1" s="79"/>
-      <c r="BF1" s="79"/>
-      <c r="BG1" s="79"/>
-      <c r="BH1" s="79"/>
-      <c r="BI1" s="79"/>
-      <c r="BJ1" s="79"/>
-      <c r="BK1" s="79"/>
-      <c r="BL1" s="80"/>
-      <c r="BM1" s="78" t="s">
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
+      <c r="AM1" s="78"/>
+      <c r="AN1" s="78"/>
+      <c r="AO1" s="78"/>
+      <c r="AP1" s="78"/>
+      <c r="AQ1" s="78"/>
+      <c r="AR1" s="78"/>
+      <c r="AS1" s="78"/>
+      <c r="AT1" s="78"/>
+      <c r="AU1" s="78"/>
+      <c r="AV1" s="78"/>
+      <c r="AW1" s="78"/>
+      <c r="AX1" s="78"/>
+      <c r="AY1" s="78"/>
+      <c r="AZ1" s="78"/>
+      <c r="BA1" s="78"/>
+      <c r="BB1" s="78"/>
+      <c r="BC1" s="78"/>
+      <c r="BD1" s="78"/>
+      <c r="BE1" s="78"/>
+      <c r="BF1" s="78"/>
+      <c r="BG1" s="78"/>
+      <c r="BH1" s="78"/>
+      <c r="BI1" s="78"/>
+      <c r="BJ1" s="78"/>
+      <c r="BK1" s="78"/>
+      <c r="BL1" s="79"/>
+      <c r="BM1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="BN1" s="79"/>
-      <c r="BO1" s="79"/>
-      <c r="BP1" s="79"/>
-      <c r="BQ1" s="79"/>
-      <c r="BR1" s="79"/>
-      <c r="BS1" s="79"/>
-      <c r="BT1" s="79"/>
-      <c r="BU1" s="79"/>
-      <c r="BV1" s="79"/>
-      <c r="BW1" s="79"/>
-      <c r="BX1" s="79"/>
-      <c r="BY1" s="79"/>
-      <c r="BZ1" s="79"/>
-      <c r="CA1" s="79"/>
-      <c r="CB1" s="79"/>
-      <c r="CC1" s="79"/>
-      <c r="CD1" s="79"/>
-      <c r="CE1" s="79"/>
-      <c r="CF1" s="79"/>
-      <c r="CG1" s="79"/>
-      <c r="CH1" s="79"/>
-      <c r="CI1" s="79"/>
-      <c r="CJ1" s="79"/>
-      <c r="CK1" s="79"/>
-      <c r="CL1" s="79"/>
-      <c r="CM1" s="79"/>
-      <c r="CN1" s="79"/>
-      <c r="CO1" s="79"/>
-      <c r="CP1" s="79"/>
-      <c r="CQ1" s="80"/>
-      <c r="CR1" s="78" t="s">
+      <c r="BN1" s="78"/>
+      <c r="BO1" s="78"/>
+      <c r="BP1" s="78"/>
+      <c r="BQ1" s="78"/>
+      <c r="BR1" s="78"/>
+      <c r="BS1" s="78"/>
+      <c r="BT1" s="78"/>
+      <c r="BU1" s="78"/>
+      <c r="BV1" s="78"/>
+      <c r="BW1" s="78"/>
+      <c r="BX1" s="78"/>
+      <c r="BY1" s="78"/>
+      <c r="BZ1" s="78"/>
+      <c r="CA1" s="78"/>
+      <c r="CB1" s="78"/>
+      <c r="CC1" s="78"/>
+      <c r="CD1" s="78"/>
+      <c r="CE1" s="78"/>
+      <c r="CF1" s="78"/>
+      <c r="CG1" s="78"/>
+      <c r="CH1" s="78"/>
+      <c r="CI1" s="78"/>
+      <c r="CJ1" s="78"/>
+      <c r="CK1" s="78"/>
+      <c r="CL1" s="78"/>
+      <c r="CM1" s="78"/>
+      <c r="CN1" s="78"/>
+      <c r="CO1" s="78"/>
+      <c r="CP1" s="78"/>
+      <c r="CQ1" s="79"/>
+      <c r="CR1" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="CS1" s="79"/>
-      <c r="CT1" s="79"/>
-      <c r="CU1" s="79"/>
-      <c r="CV1" s="79"/>
-      <c r="CW1" s="79"/>
-      <c r="CX1" s="79"/>
-      <c r="CY1" s="79"/>
-      <c r="CZ1" s="79"/>
-      <c r="DA1" s="79"/>
-      <c r="DB1" s="79"/>
-      <c r="DC1" s="79"/>
-      <c r="DD1" s="79"/>
-      <c r="DE1" s="79"/>
-      <c r="DF1" s="79"/>
-      <c r="DG1" s="79"/>
-      <c r="DH1" s="79"/>
-      <c r="DI1" s="79"/>
-      <c r="DJ1" s="79"/>
-      <c r="DK1" s="79"/>
-      <c r="DL1" s="79"/>
-      <c r="DM1" s="79"/>
-      <c r="DN1" s="79"/>
-      <c r="DO1" s="79"/>
-      <c r="DP1" s="79"/>
-      <c r="DQ1" s="79"/>
-      <c r="DR1" s="79"/>
-      <c r="DS1" s="79"/>
-      <c r="DT1" s="79"/>
-      <c r="DU1" s="79"/>
-      <c r="DV1" s="80"/>
-      <c r="DW1" s="78" t="s">
+      <c r="CS1" s="78"/>
+      <c r="CT1" s="78"/>
+      <c r="CU1" s="78"/>
+      <c r="CV1" s="78"/>
+      <c r="CW1" s="78"/>
+      <c r="CX1" s="78"/>
+      <c r="CY1" s="78"/>
+      <c r="CZ1" s="78"/>
+      <c r="DA1" s="78"/>
+      <c r="DB1" s="78"/>
+      <c r="DC1" s="78"/>
+      <c r="DD1" s="78"/>
+      <c r="DE1" s="78"/>
+      <c r="DF1" s="78"/>
+      <c r="DG1" s="78"/>
+      <c r="DH1" s="78"/>
+      <c r="DI1" s="78"/>
+      <c r="DJ1" s="78"/>
+      <c r="DK1" s="78"/>
+      <c r="DL1" s="78"/>
+      <c r="DM1" s="78"/>
+      <c r="DN1" s="78"/>
+      <c r="DO1" s="78"/>
+      <c r="DP1" s="78"/>
+      <c r="DQ1" s="78"/>
+      <c r="DR1" s="78"/>
+      <c r="DS1" s="78"/>
+      <c r="DT1" s="78"/>
+      <c r="DU1" s="78"/>
+      <c r="DV1" s="79"/>
+      <c r="DW1" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="DX1" s="79"/>
-      <c r="DY1" s="79"/>
-      <c r="DZ1" s="79"/>
-      <c r="EA1" s="79"/>
-      <c r="EB1" s="79"/>
-      <c r="EC1" s="79"/>
-      <c r="ED1" s="79"/>
-      <c r="EE1" s="79"/>
-      <c r="EF1" s="79"/>
-      <c r="EG1" s="79"/>
-      <c r="EH1" s="79"/>
-      <c r="EI1" s="79"/>
-      <c r="EJ1" s="79"/>
-      <c r="EK1" s="79"/>
-      <c r="EL1" s="79"/>
-      <c r="EM1" s="79"/>
-      <c r="EN1" s="79"/>
-      <c r="EO1" s="79"/>
-      <c r="EP1" s="79"/>
-      <c r="EQ1" s="79"/>
-      <c r="ER1" s="79"/>
-      <c r="ES1" s="79"/>
-      <c r="ET1" s="79"/>
-      <c r="EU1" s="79"/>
-      <c r="EV1" s="79"/>
-      <c r="EW1" s="79"/>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="78" t="s">
+      <c r="DX1" s="78"/>
+      <c r="DY1" s="78"/>
+      <c r="DZ1" s="78"/>
+      <c r="EA1" s="78"/>
+      <c r="EB1" s="78"/>
+      <c r="EC1" s="78"/>
+      <c r="ED1" s="78"/>
+      <c r="EE1" s="78"/>
+      <c r="EF1" s="78"/>
+      <c r="EG1" s="78"/>
+      <c r="EH1" s="78"/>
+      <c r="EI1" s="78"/>
+      <c r="EJ1" s="78"/>
+      <c r="EK1" s="78"/>
+      <c r="EL1" s="78"/>
+      <c r="EM1" s="78"/>
+      <c r="EN1" s="78"/>
+      <c r="EO1" s="78"/>
+      <c r="EP1" s="78"/>
+      <c r="EQ1" s="78"/>
+      <c r="ER1" s="78"/>
+      <c r="ES1" s="78"/>
+      <c r="ET1" s="78"/>
+      <c r="EU1" s="78"/>
+      <c r="EV1" s="78"/>
+      <c r="EW1" s="78"/>
+      <c r="EX1" s="78"/>
+      <c r="EY1" s="78"/>
+      <c r="EZ1" s="78"/>
+      <c r="FA1" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="79"/>
-      <c r="GA1" s="79"/>
-      <c r="GB1" s="79"/>
-      <c r="GC1" s="79"/>
-      <c r="GD1" s="79"/>
-      <c r="GE1" s="80"/>
-      <c r="GF1" s="78" t="s">
+      <c r="FB1" s="78"/>
+      <c r="FC1" s="78"/>
+      <c r="FD1" s="78"/>
+      <c r="FE1" s="78"/>
+      <c r="FF1" s="78"/>
+      <c r="FG1" s="78"/>
+      <c r="FH1" s="78"/>
+      <c r="FI1" s="78"/>
+      <c r="FJ1" s="78"/>
+      <c r="FK1" s="78"/>
+      <c r="FL1" s="78"/>
+      <c r="FM1" s="78"/>
+      <c r="FN1" s="78"/>
+      <c r="FO1" s="78"/>
+      <c r="FP1" s="78"/>
+      <c r="FQ1" s="78"/>
+      <c r="FR1" s="78"/>
+      <c r="FS1" s="78"/>
+      <c r="FT1" s="78"/>
+      <c r="FU1" s="78"/>
+      <c r="FV1" s="78"/>
+      <c r="FW1" s="78"/>
+      <c r="FX1" s="78"/>
+      <c r="FY1" s="78"/>
+      <c r="FZ1" s="78"/>
+      <c r="GA1" s="78"/>
+      <c r="GB1" s="78"/>
+      <c r="GC1" s="78"/>
+      <c r="GD1" s="78"/>
+      <c r="GE1" s="79"/>
+      <c r="GF1" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="GG1" s="79"/>
-      <c r="GH1" s="79"/>
-      <c r="GI1" s="79"/>
-      <c r="GJ1" s="79"/>
-      <c r="GK1" s="79"/>
-      <c r="GL1" s="79"/>
-      <c r="GM1" s="79"/>
-      <c r="GN1" s="79"/>
-      <c r="GO1" s="79"/>
-      <c r="GP1" s="79"/>
-      <c r="GQ1" s="79"/>
-      <c r="GR1" s="79"/>
-      <c r="GS1" s="79"/>
-      <c r="GT1" s="79"/>
-      <c r="GU1" s="79"/>
-      <c r="GV1" s="79"/>
-      <c r="GW1" s="79"/>
-      <c r="GX1" s="79"/>
-      <c r="GY1" s="79"/>
-      <c r="GZ1" s="79"/>
-      <c r="HA1" s="79"/>
-      <c r="HB1" s="79"/>
-      <c r="HC1" s="79"/>
-      <c r="HD1" s="79"/>
-      <c r="HE1" s="79"/>
-      <c r="HF1" s="79"/>
-      <c r="HG1" s="79"/>
-      <c r="HH1" s="79"/>
-      <c r="HI1" s="79"/>
-      <c r="HJ1" s="78" t="s">
+      <c r="GG1" s="78"/>
+      <c r="GH1" s="78"/>
+      <c r="GI1" s="78"/>
+      <c r="GJ1" s="78"/>
+      <c r="GK1" s="78"/>
+      <c r="GL1" s="78"/>
+      <c r="GM1" s="78"/>
+      <c r="GN1" s="78"/>
+      <c r="GO1" s="78"/>
+      <c r="GP1" s="78"/>
+      <c r="GQ1" s="78"/>
+      <c r="GR1" s="78"/>
+      <c r="GS1" s="78"/>
+      <c r="GT1" s="78"/>
+      <c r="GU1" s="78"/>
+      <c r="GV1" s="78"/>
+      <c r="GW1" s="78"/>
+      <c r="GX1" s="78"/>
+      <c r="GY1" s="78"/>
+      <c r="GZ1" s="78"/>
+      <c r="HA1" s="78"/>
+      <c r="HB1" s="78"/>
+      <c r="HC1" s="78"/>
+      <c r="HD1" s="78"/>
+      <c r="HE1" s="78"/>
+      <c r="HF1" s="78"/>
+      <c r="HG1" s="78"/>
+      <c r="HH1" s="78"/>
+      <c r="HI1" s="78"/>
+      <c r="HJ1" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="HK1" s="79"/>
-      <c r="HL1" s="79"/>
-      <c r="HM1" s="79"/>
-      <c r="HN1" s="79"/>
-      <c r="HO1" s="79"/>
-      <c r="HP1" s="79"/>
-      <c r="HQ1" s="79"/>
-      <c r="HR1" s="79"/>
-      <c r="HS1" s="79"/>
-      <c r="HT1" s="79"/>
-      <c r="HU1" s="79"/>
-      <c r="HV1" s="79"/>
-      <c r="HW1" s="79"/>
-      <c r="HX1" s="79"/>
-      <c r="HY1" s="79"/>
-      <c r="HZ1" s="79"/>
-      <c r="IA1" s="79"/>
-      <c r="IB1" s="79"/>
-      <c r="IC1" s="79"/>
-      <c r="ID1" s="79"/>
-      <c r="IE1" s="79"/>
-      <c r="IF1" s="79"/>
-      <c r="IG1" s="79"/>
-      <c r="IH1" s="79"/>
-      <c r="II1" s="79"/>
-      <c r="IJ1" s="79"/>
-      <c r="IK1" s="79"/>
-      <c r="IL1" s="79"/>
-      <c r="IM1" s="79"/>
-      <c r="IN1" s="80"/>
-      <c r="IO1" s="78" t="s">
+      <c r="HK1" s="78"/>
+      <c r="HL1" s="78"/>
+      <c r="HM1" s="78"/>
+      <c r="HN1" s="78"/>
+      <c r="HO1" s="78"/>
+      <c r="HP1" s="78"/>
+      <c r="HQ1" s="78"/>
+      <c r="HR1" s="78"/>
+      <c r="HS1" s="78"/>
+      <c r="HT1" s="78"/>
+      <c r="HU1" s="78"/>
+      <c r="HV1" s="78"/>
+      <c r="HW1" s="78"/>
+      <c r="HX1" s="78"/>
+      <c r="HY1" s="78"/>
+      <c r="HZ1" s="78"/>
+      <c r="IA1" s="78"/>
+      <c r="IB1" s="78"/>
+      <c r="IC1" s="78"/>
+      <c r="ID1" s="78"/>
+      <c r="IE1" s="78"/>
+      <c r="IF1" s="78"/>
+      <c r="IG1" s="78"/>
+      <c r="IH1" s="78"/>
+      <c r="II1" s="78"/>
+      <c r="IJ1" s="78"/>
+      <c r="IK1" s="78"/>
+      <c r="IL1" s="78"/>
+      <c r="IM1" s="78"/>
+      <c r="IN1" s="79"/>
+      <c r="IO1" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="IP1" s="79"/>
-      <c r="IQ1" s="79"/>
-      <c r="IR1" s="79"/>
-      <c r="IS1" s="79"/>
-      <c r="IT1" s="79"/>
-      <c r="IU1" s="79"/>
-      <c r="IV1" s="79"/>
-      <c r="IW1" s="79"/>
-      <c r="IX1" s="79"/>
-      <c r="IY1" s="79"/>
-      <c r="IZ1" s="79"/>
-      <c r="JA1" s="79"/>
-      <c r="JB1" s="79"/>
-      <c r="JC1" s="79"/>
-      <c r="JD1" s="79"/>
-      <c r="JE1" s="79"/>
-      <c r="JF1" s="79"/>
-      <c r="JG1" s="79"/>
-      <c r="JH1" s="79"/>
-      <c r="JI1" s="79"/>
-      <c r="JJ1" s="79"/>
-      <c r="JK1" s="79"/>
-      <c r="JL1" s="79"/>
-      <c r="JM1" s="79"/>
-      <c r="JN1" s="79"/>
-      <c r="JO1" s="79"/>
-      <c r="JP1" s="79"/>
-      <c r="JQ1" s="79"/>
-      <c r="JR1" s="79"/>
-      <c r="JS1" s="80"/>
-      <c r="JT1" s="78" t="s">
+      <c r="IP1" s="78"/>
+      <c r="IQ1" s="78"/>
+      <c r="IR1" s="78"/>
+      <c r="IS1" s="78"/>
+      <c r="IT1" s="78"/>
+      <c r="IU1" s="78"/>
+      <c r="IV1" s="78"/>
+      <c r="IW1" s="78"/>
+      <c r="IX1" s="78"/>
+      <c r="IY1" s="78"/>
+      <c r="IZ1" s="78"/>
+      <c r="JA1" s="78"/>
+      <c r="JB1" s="78"/>
+      <c r="JC1" s="78"/>
+      <c r="JD1" s="78"/>
+      <c r="JE1" s="78"/>
+      <c r="JF1" s="78"/>
+      <c r="JG1" s="78"/>
+      <c r="JH1" s="78"/>
+      <c r="JI1" s="78"/>
+      <c r="JJ1" s="78"/>
+      <c r="JK1" s="78"/>
+      <c r="JL1" s="78"/>
+      <c r="JM1" s="78"/>
+      <c r="JN1" s="78"/>
+      <c r="JO1" s="78"/>
+      <c r="JP1" s="78"/>
+      <c r="JQ1" s="78"/>
+      <c r="JR1" s="78"/>
+      <c r="JS1" s="79"/>
+      <c r="JT1" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="JU1" s="79"/>
-      <c r="JV1" s="79"/>
-      <c r="JW1" s="79"/>
-      <c r="JX1" s="79"/>
-      <c r="JY1" s="79"/>
-      <c r="JZ1" s="79"/>
-      <c r="KA1" s="79"/>
-      <c r="KB1" s="79"/>
-      <c r="KC1" s="79"/>
-      <c r="KD1" s="79"/>
-      <c r="KE1" s="79"/>
-      <c r="KF1" s="79"/>
-      <c r="KG1" s="79"/>
-      <c r="KH1" s="79"/>
-      <c r="KI1" s="79"/>
-      <c r="KJ1" s="79"/>
-      <c r="KK1" s="79"/>
-      <c r="KL1" s="79"/>
-      <c r="KM1" s="79"/>
-      <c r="KN1" s="79"/>
-      <c r="KO1" s="79"/>
-      <c r="KP1" s="79"/>
-      <c r="KQ1" s="79"/>
-      <c r="KR1" s="79"/>
-      <c r="KS1" s="79"/>
-      <c r="KT1" s="79"/>
-      <c r="KU1" s="79"/>
+      <c r="JU1" s="78"/>
+      <c r="JV1" s="78"/>
+      <c r="JW1" s="78"/>
+      <c r="JX1" s="78"/>
+      <c r="JY1" s="78"/>
+      <c r="JZ1" s="78"/>
+      <c r="KA1" s="78"/>
+      <c r="KB1" s="78"/>
+      <c r="KC1" s="78"/>
+      <c r="KD1" s="78"/>
+      <c r="KE1" s="78"/>
+      <c r="KF1" s="78"/>
+      <c r="KG1" s="78"/>
+      <c r="KH1" s="78"/>
+      <c r="KI1" s="78"/>
+      <c r="KJ1" s="78"/>
+      <c r="KK1" s="78"/>
+      <c r="KL1" s="78"/>
+      <c r="KM1" s="78"/>
+      <c r="KN1" s="78"/>
+      <c r="KO1" s="78"/>
+      <c r="KP1" s="78"/>
+      <c r="KQ1" s="78"/>
+      <c r="KR1" s="78"/>
+      <c r="KS1" s="78"/>
+      <c r="KT1" s="78"/>
+      <c r="KU1" s="78"/>
     </row>
     <row r="2" spans="1:307" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -1684,10 +1694,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G2" s="69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
@@ -2592,7 +2602,7 @@
     </row>
     <row r="3" spans="1:307" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -6256,7 +6266,7 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="14">
@@ -10497,7 +10507,7 @@
     </row>
     <row r="26" spans="1:307" ht="15.75" customHeight="1">
       <c r="A26" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -11690,7 +11700,7 @@
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E28" s="29" t="s">
         <v>38</v>
@@ -12401,30 +12411,21 @@
       <c r="KT29" s="23"/>
       <c r="KU29" s="23"/>
     </row>
-    <row r="30" spans="1:307" ht="15.75" customHeight="1">
+    <row r="30" spans="1:307" ht="15" customHeight="1">
       <c r="A30" s="27">
         <v>4</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30">
-        <v>46177</v>
-      </c>
-      <c r="G30" s="30">
-        <v>46208</v>
-      </c>
-      <c r="H30" s="31">
-        <v>0</v>
-      </c>
-      <c r="I30" s="29"/>
+        <v>105</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
       <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
       <c r="L30" s="32"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
@@ -12462,284 +12463,27 @@
       <c r="AT30" s="23"/>
       <c r="AU30" s="23"/>
       <c r="AV30" s="23"/>
-      <c r="AW30" s="23"/>
-      <c r="AX30" s="23"/>
-      <c r="AY30" s="23"/>
-      <c r="AZ30" s="66"/>
-      <c r="BA30" s="66"/>
       <c r="BB30" s="66"/>
       <c r="BC30" s="66"/>
-      <c r="BD30" s="66"/>
-      <c r="BE30" s="66"/>
-      <c r="BF30" s="66"/>
-      <c r="BG30" s="66"/>
-      <c r="BH30" s="23"/>
       <c r="BI30" s="23"/>
       <c r="BJ30" s="23"/>
-      <c r="BK30" s="23"/>
-      <c r="BL30" s="23"/>
-      <c r="BM30" s="23"/>
-      <c r="BN30" s="23"/>
-      <c r="BO30" s="23"/>
       <c r="BP30" s="23"/>
       <c r="BQ30" s="23"/>
-      <c r="BR30" s="23"/>
-      <c r="BS30" s="23"/>
-      <c r="BT30" s="23"/>
-      <c r="BU30" s="23"/>
-      <c r="BV30" s="23"/>
       <c r="BW30" s="23"/>
       <c r="BX30" s="23"/>
-      <c r="BY30" s="23"/>
-      <c r="BZ30" s="23"/>
-      <c r="CA30" s="23"/>
-      <c r="CB30" s="23"/>
-      <c r="CC30" s="23"/>
-      <c r="CD30" s="23"/>
-      <c r="CE30" s="23"/>
-      <c r="CF30" s="23"/>
-      <c r="CG30" s="23"/>
-      <c r="CH30" s="23"/>
-      <c r="CI30" s="23"/>
-      <c r="CJ30" s="23"/>
-      <c r="CK30" s="23"/>
-      <c r="CL30" s="23"/>
-      <c r="CM30" s="23"/>
-      <c r="CN30" s="23"/>
-      <c r="CO30" s="23"/>
-      <c r="CP30" s="23"/>
-      <c r="CQ30" s="23"/>
-      <c r="CR30" s="23"/>
-      <c r="CS30" s="23"/>
-      <c r="CT30" s="23"/>
-      <c r="CU30" s="23"/>
-      <c r="CV30" s="23"/>
-      <c r="CW30" s="23"/>
-      <c r="CX30" s="23"/>
-      <c r="CY30" s="23"/>
-      <c r="CZ30" s="23"/>
-      <c r="DA30" s="23"/>
-      <c r="DB30" s="23"/>
-      <c r="DC30" s="23"/>
-      <c r="DD30" s="23"/>
-      <c r="DE30" s="23"/>
-      <c r="DF30" s="23"/>
-      <c r="DG30" s="23"/>
-      <c r="DH30" s="23"/>
-      <c r="DI30" s="23"/>
-      <c r="DJ30" s="23"/>
-      <c r="DK30" s="23"/>
-      <c r="DL30" s="23"/>
-      <c r="DM30" s="23"/>
-      <c r="DN30" s="23"/>
-      <c r="DO30" s="23"/>
-      <c r="DP30" s="23"/>
-      <c r="DQ30" s="23"/>
-      <c r="DR30" s="23"/>
-      <c r="DS30" s="23"/>
-      <c r="DT30" s="23"/>
-      <c r="DU30" s="23"/>
-      <c r="DV30" s="23"/>
-      <c r="DW30" s="23"/>
-      <c r="DX30" s="23"/>
-      <c r="DY30" s="23"/>
-      <c r="DZ30" s="23"/>
-      <c r="EA30" s="23"/>
-      <c r="EB30" s="23"/>
-      <c r="EC30" s="23"/>
-      <c r="ED30" s="23"/>
-      <c r="EE30" s="23"/>
-      <c r="EF30" s="23"/>
-      <c r="EG30" s="23"/>
-      <c r="EH30" s="23"/>
-      <c r="EI30" s="23"/>
-      <c r="EJ30" s="23"/>
-      <c r="EK30" s="23"/>
-      <c r="EL30" s="23"/>
-      <c r="EM30" s="23"/>
-      <c r="EN30" s="23"/>
-      <c r="EO30" s="23"/>
-      <c r="EP30" s="23"/>
-      <c r="EQ30" s="23"/>
-      <c r="ER30" s="23"/>
-      <c r="ES30" s="23"/>
-      <c r="ET30" s="23"/>
-      <c r="EU30" s="23"/>
-      <c r="EV30" s="23"/>
-      <c r="EW30" s="23"/>
-      <c r="EX30" s="23"/>
-      <c r="EY30" s="23"/>
-      <c r="EZ30" s="23"/>
-      <c r="FA30" s="23"/>
-      <c r="FB30" s="23"/>
-      <c r="FC30" s="23"/>
-      <c r="FD30" s="23"/>
-      <c r="FE30" s="23"/>
-      <c r="FF30" s="23"/>
-      <c r="FG30" s="23"/>
-      <c r="FH30" s="23"/>
-      <c r="FI30" s="23"/>
-      <c r="FJ30" s="23"/>
-      <c r="FK30" s="23"/>
-      <c r="FL30" s="23"/>
-      <c r="FM30" s="23"/>
-      <c r="FN30" s="23"/>
-      <c r="FO30" s="23"/>
-      <c r="FP30" s="23"/>
-      <c r="FQ30" s="23"/>
-      <c r="FR30" s="23"/>
-      <c r="FS30" s="23"/>
-      <c r="FT30" s="23"/>
-      <c r="FU30" s="23"/>
-      <c r="FV30" s="23"/>
-      <c r="FW30" s="23"/>
-      <c r="FX30" s="23"/>
-      <c r="FY30" s="23"/>
-      <c r="FZ30" s="23"/>
-      <c r="GA30" s="23"/>
-      <c r="GB30" s="23"/>
-      <c r="GC30" s="23"/>
-      <c r="GD30" s="23"/>
-      <c r="GE30" s="23"/>
-      <c r="GF30" s="23"/>
-      <c r="GG30" s="23"/>
-      <c r="GH30" s="23"/>
-      <c r="GI30" s="23"/>
-      <c r="GJ30" s="23"/>
-      <c r="GK30" s="23"/>
-      <c r="GL30" s="23"/>
-      <c r="GM30" s="23"/>
-      <c r="GN30" s="23"/>
-      <c r="GO30" s="23"/>
-      <c r="GP30" s="23"/>
-      <c r="GQ30" s="23"/>
-      <c r="GR30" s="23"/>
-      <c r="GS30" s="23"/>
-      <c r="GT30" s="23"/>
-      <c r="GU30" s="23"/>
-      <c r="GV30" s="23"/>
-      <c r="GW30" s="23"/>
-      <c r="GX30" s="23"/>
-      <c r="GY30" s="23"/>
-      <c r="GZ30" s="23"/>
-      <c r="HA30" s="23"/>
-      <c r="HB30" s="23"/>
-      <c r="HC30" s="23"/>
-      <c r="HD30" s="23"/>
-      <c r="HE30" s="23"/>
-      <c r="HF30" s="23"/>
-      <c r="HG30" s="23"/>
-      <c r="HH30" s="23"/>
-      <c r="HI30" s="23"/>
-      <c r="HJ30" s="23"/>
-      <c r="HK30" s="23"/>
-      <c r="HL30" s="23"/>
-      <c r="HM30" s="23"/>
-      <c r="HN30" s="23"/>
-      <c r="HO30" s="23"/>
-      <c r="HP30" s="23"/>
-      <c r="HQ30" s="23"/>
-      <c r="HR30" s="23"/>
-      <c r="HS30" s="23"/>
-      <c r="HT30" s="23"/>
-      <c r="HU30" s="23"/>
-      <c r="HV30" s="23"/>
-      <c r="HW30" s="23"/>
-      <c r="HX30" s="23"/>
-      <c r="HY30" s="23"/>
-      <c r="HZ30" s="23"/>
-      <c r="IA30" s="23"/>
-      <c r="IB30" s="23"/>
-      <c r="IC30" s="23"/>
-      <c r="ID30" s="23"/>
-      <c r="IE30" s="23"/>
-      <c r="IF30" s="23"/>
-      <c r="IG30" s="23"/>
-      <c r="IH30" s="23"/>
-      <c r="II30" s="23"/>
-      <c r="IJ30" s="23"/>
-      <c r="IK30" s="23"/>
-      <c r="IL30" s="23"/>
-      <c r="IM30" s="23"/>
-      <c r="IN30" s="23"/>
-      <c r="IO30" s="23"/>
-      <c r="IP30" s="23"/>
-      <c r="IQ30" s="23"/>
-      <c r="IR30" s="23"/>
-      <c r="IS30" s="23"/>
-      <c r="IT30" s="23"/>
-      <c r="IU30" s="23"/>
-      <c r="IV30" s="23"/>
-      <c r="IW30" s="23"/>
-      <c r="IX30" s="23"/>
-      <c r="IY30" s="23"/>
-      <c r="IZ30" s="23"/>
-      <c r="JA30" s="23"/>
-      <c r="JB30" s="23"/>
-      <c r="JC30" s="23"/>
-      <c r="JD30" s="23"/>
-      <c r="JE30" s="23"/>
-      <c r="JF30" s="23"/>
-      <c r="JG30" s="23"/>
-      <c r="JH30" s="23"/>
-      <c r="JI30" s="23"/>
-      <c r="JJ30" s="23"/>
-      <c r="JK30" s="23"/>
-      <c r="JL30" s="23"/>
-      <c r="JM30" s="23"/>
-      <c r="JN30" s="23"/>
-      <c r="JO30" s="23"/>
-      <c r="JP30" s="23"/>
-      <c r="JQ30" s="23"/>
-      <c r="JR30" s="23"/>
-      <c r="JS30" s="23"/>
-      <c r="JT30" s="23"/>
-      <c r="JU30" s="23"/>
-      <c r="JV30" s="23"/>
-      <c r="JW30" s="23"/>
-      <c r="JX30" s="23"/>
-      <c r="JY30" s="23"/>
-      <c r="JZ30" s="23"/>
-      <c r="KA30" s="23"/>
-      <c r="KB30" s="23"/>
-      <c r="KC30" s="23"/>
-      <c r="KD30" s="23"/>
-      <c r="KE30" s="23"/>
-      <c r="KF30" s="23"/>
-      <c r="KG30" s="23"/>
-      <c r="KH30" s="23"/>
-      <c r="KI30" s="23"/>
-      <c r="KJ30" s="23"/>
-      <c r="KK30" s="23"/>
-      <c r="KL30" s="23"/>
-      <c r="KM30" s="23"/>
-      <c r="KN30" s="23"/>
-      <c r="KO30" s="23"/>
-      <c r="KP30" s="23"/>
-      <c r="KQ30" s="23"/>
-      <c r="KR30" s="23"/>
-      <c r="KS30" s="23"/>
-      <c r="KT30" s="23"/>
-      <c r="KU30" s="23"/>
     </row>
     <row r="31" spans="1:307" ht="15.75" customHeight="1">
       <c r="A31" s="27">
         <v>5</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="29"/>
-      <c r="D31" s="73" t="s">
-        <v>106</v>
-      </c>
+      <c r="D31" s="29"/>
       <c r="E31" s="29"/>
-      <c r="F31" s="30">
-        <v>46209</v>
-      </c>
-      <c r="G31" s="30">
-        <v>46212</v>
-      </c>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="31">
         <v>0</v>
       </c>
@@ -13048,15 +12792,21 @@
         <v>6</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
+      <c r="D32" s="70" t="s">
+        <v>104</v>
+      </c>
       <c r="E32" s="29"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
+      <c r="F32" s="30">
+        <v>46191</v>
+      </c>
+      <c r="G32" s="30">
+        <v>46191</v>
+      </c>
       <c r="H32" s="31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="32"/>
@@ -13101,14 +12851,16 @@
       <c r="AW32" s="23"/>
       <c r="AX32" s="23"/>
       <c r="AY32" s="23"/>
-      <c r="AZ32" s="66"/>
-      <c r="BA32" s="66"/>
-      <c r="BB32" s="66"/>
-      <c r="BC32" s="66"/>
-      <c r="BD32" s="66"/>
-      <c r="BE32" s="66"/>
-      <c r="BF32" s="66"/>
-      <c r="BG32" s="66"/>
+      <c r="AZ32" s="66" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA32" s="22"/>
+      <c r="BB32" s="23"/>
+      <c r="BC32" s="23"/>
+      <c r="BD32" s="23"/>
+      <c r="BE32" s="23"/>
+      <c r="BF32" s="23"/>
+      <c r="BG32" s="23"/>
       <c r="BH32" s="23"/>
       <c r="BI32" s="23"/>
       <c r="BJ32" s="23"/>
@@ -13363,11 +13115,11 @@
         <v>7</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" s="29"/>
-      <c r="D33" s="70" t="s">
-        <v>106</v>
+      <c r="D33" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="30">
@@ -13425,7 +13177,7 @@
       <c r="AZ33" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="BA33" s="22"/>
+      <c r="BA33" s="23"/>
       <c r="BB33" s="23"/>
       <c r="BC33" s="23"/>
       <c r="BD33" s="23"/>
@@ -13686,7 +13438,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" s="29"/>
       <c r="D34" s="29" t="s">
@@ -13697,7 +13449,7 @@
         <v>46191</v>
       </c>
       <c r="G34" s="30">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="H34" s="31">
         <v>1</v>
@@ -13748,10 +13500,18 @@
       <c r="AZ34" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="BA34" s="23"/>
-      <c r="BB34" s="23"/>
-      <c r="BC34" s="23"/>
-      <c r="BD34" s="23"/>
+      <c r="BA34" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC34" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="66" t="b">
+        <v>1</v>
+      </c>
       <c r="BE34" s="23"/>
       <c r="BF34" s="23"/>
       <c r="BG34" s="23"/>
@@ -14009,7 +13769,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C35" s="29"/>
       <c r="D35" s="29" t="s">
@@ -14022,9 +13782,7 @@
       <c r="G35" s="30">
         <v>46195</v>
       </c>
-      <c r="H35" s="31">
-        <v>1</v>
-      </c>
+      <c r="H35" s="31"/>
       <c r="I35" s="29"/>
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
@@ -14340,7 +14098,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C36" s="29"/>
       <c r="D36" s="29" t="s">
@@ -14348,12 +14106,14 @@
       </c>
       <c r="E36" s="29"/>
       <c r="F36" s="30">
-        <v>46191</v>
+        <v>46226</v>
       </c>
       <c r="G36" s="30">
-        <v>46195</v>
-      </c>
-      <c r="H36" s="31"/>
+        <v>46226</v>
+      </c>
+      <c r="H36" s="31">
+        <v>0</v>
+      </c>
       <c r="I36" s="29"/>
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
@@ -14397,35 +14157,55 @@
       <c r="AW36" s="23"/>
       <c r="AX36" s="23"/>
       <c r="AY36" s="23"/>
-      <c r="AZ36" s="66" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA36" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB36" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC36" s="66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AZ36" s="23"/>
+      <c r="BA36" s="23"/>
+      <c r="BB36" s="23"/>
+      <c r="BC36" s="23"/>
       <c r="BD36" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="BE36" s="23"/>
-      <c r="BF36" s="23"/>
-      <c r="BG36" s="23"/>
-      <c r="BH36" s="23"/>
-      <c r="BI36" s="23"/>
-      <c r="BJ36" s="23"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23"/>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36" s="23"/>
-      <c r="BQ36" s="23"/>
-      <c r="BR36" s="23"/>
+      <c r="BE36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG36" s="66" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ36" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR36" s="66" t="b">
+        <v>0</v>
+      </c>
       <c r="BS36" s="23"/>
       <c r="BT36" s="23"/>
       <c r="BU36" s="23"/>
@@ -14669,20 +14449,22 @@
         <v>11</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C37" s="29"/>
-      <c r="D37" s="29" t="s">
-        <v>50</v>
+      <c r="D37" s="71" t="s">
+        <v>84</v>
       </c>
       <c r="E37" s="29"/>
       <c r="F37" s="30">
-        <v>46191</v>
+        <v>46177</v>
       </c>
       <c r="G37" s="30">
-        <v>46195</v>
-      </c>
-      <c r="H37" s="31"/>
+        <v>46226</v>
+      </c>
+      <c r="H37" s="31">
+        <v>0</v>
+      </c>
       <c r="I37" s="29"/>
       <c r="J37" s="32"/>
       <c r="K37" s="32"/>
@@ -14726,24 +14508,14 @@
       <c r="AW37" s="23"/>
       <c r="AX37" s="23"/>
       <c r="AY37" s="23"/>
-      <c r="AZ37" s="66" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA37" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB37" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC37" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD37" s="66" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE37" s="23"/>
-      <c r="BF37" s="23"/>
-      <c r="BG37" s="23"/>
+      <c r="AZ37" s="66"/>
+      <c r="BA37" s="66"/>
+      <c r="BB37" s="66"/>
+      <c r="BC37" s="66"/>
+      <c r="BD37" s="66"/>
+      <c r="BE37" s="66"/>
+      <c r="BF37" s="66"/>
+      <c r="BG37" s="66"/>
       <c r="BH37" s="23"/>
       <c r="BI37" s="23"/>
       <c r="BJ37" s="23"/>
@@ -14998,7 +14770,7 @@
         <v>12</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29" t="s">
@@ -15006,14 +14778,12 @@
       </c>
       <c r="E38" s="29"/>
       <c r="F38" s="30">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="G38" s="30">
-        <v>46209</v>
-      </c>
-      <c r="H38" s="31">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="H38" s="31"/>
       <c r="I38" s="29"/>
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
@@ -15057,55 +14827,35 @@
       <c r="AW38" s="23"/>
       <c r="AX38" s="23"/>
       <c r="AY38" s="23"/>
-      <c r="AZ38" s="23"/>
-      <c r="BA38" s="23"/>
-      <c r="BB38" s="23"/>
-      <c r="BC38" s="23"/>
+      <c r="AZ38" s="66" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA38" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB38" s="66" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC38" s="66" t="b">
+        <v>0</v>
+      </c>
       <c r="BD38" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="BE38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG38" s="66" t="b">
-        <v>1</v>
-      </c>
-      <c r="BH38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BK38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BL38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BM38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BN38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BQ38" s="66" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR38" s="66" t="b">
-        <v>0</v>
-      </c>
+      <c r="BE38" s="23"/>
+      <c r="BF38" s="23"/>
+      <c r="BG38" s="23"/>
+      <c r="BH38" s="23"/>
+      <c r="BI38" s="23"/>
+      <c r="BJ38" s="23"/>
+      <c r="BK38" s="23"/>
+      <c r="BL38" s="23"/>
+      <c r="BM38" s="23"/>
+      <c r="BN38" s="23"/>
+      <c r="BO38" s="23"/>
+      <c r="BP38" s="23"/>
+      <c r="BQ38" s="23"/>
+      <c r="BR38" s="23"/>
       <c r="BS38" s="23"/>
       <c r="BT38" s="23"/>
       <c r="BU38" s="23"/>
@@ -15346,7 +15096,7 @@
     </row>
     <row r="39" spans="1:307" ht="15.75" customHeight="1">
       <c r="A39" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -15660,7 +15410,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="37"/>
       <c r="D40" s="37"/>
@@ -17410,7 +17160,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -18285,7 +18035,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43" s="37"/>
       <c r="D43" s="37"/>
@@ -19160,7 +18910,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -20035,7 +19785,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="37"/>
@@ -20910,7 +20660,7 @@
         <v>7</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C46" s="37"/>
       <c r="D46" s="37"/>
@@ -21225,7 +20975,7 @@
         <v>8</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C47" s="37"/>
       <c r="D47" s="37"/>
@@ -21539,8 +21289,8 @@
       <c r="A48" s="35">
         <v>9</v>
       </c>
-      <c r="B48" s="76" t="s">
-        <v>100</v>
+      <c r="B48" s="75" t="s">
+        <v>98</v>
       </c>
       <c r="C48" s="37"/>
       <c r="D48" s="37"/>
@@ -21852,8 +21602,8 @@
       <c r="A49" s="35">
         <v>10</v>
       </c>
-      <c r="B49" s="76" t="s">
-        <v>101</v>
+      <c r="B49" s="75" t="s">
+        <v>99</v>
       </c>
       <c r="C49" s="37"/>
       <c r="D49" s="37"/>
@@ -22166,7 +21916,7 @@
         <v>11</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C50" s="37"/>
       <c r="D50" s="37"/>
@@ -23041,7 +22791,7 @@
         <v>12</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C51" s="37"/>
       <c r="D51" s="37"/>
@@ -23916,7 +23666,7 @@
         <v>13</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C52" s="37"/>
       <c r="D52" s="37"/>
@@ -25100,7 +24850,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
@@ -29463,8 +29213,8 @@
       </c>
     </row>
     <row r="59" spans="1:307" ht="15.75" customHeight="1">
-      <c r="A59" s="75" t="s">
-        <v>99</v>
+      <c r="A59" s="74" t="s">
+        <v>97</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
@@ -29777,8 +29527,8 @@
       <c r="A60" s="44">
         <v>1</v>
       </c>
-      <c r="B60" s="74" t="s">
-        <v>91</v>
+      <c r="B60" s="73" t="s">
+        <v>89</v>
       </c>
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
@@ -30652,8 +30402,8 @@
       <c r="A61" s="44">
         <v>2</v>
       </c>
-      <c r="B61" s="74" t="s">
-        <v>92</v>
+      <c r="B61" s="73" t="s">
+        <v>90</v>
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
@@ -31527,8 +31277,8 @@
       <c r="A62" s="44">
         <v>3</v>
       </c>
-      <c r="B62" s="74" t="s">
-        <v>102</v>
+      <c r="B62" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="C62" s="46"/>
       <c r="D62" s="46"/>
@@ -31840,8 +31590,8 @@
       <c r="A63" s="44">
         <v>4</v>
       </c>
-      <c r="B63" s="74" t="s">
-        <v>103</v>
+      <c r="B63" s="73" t="s">
+        <v>101</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
@@ -32153,8 +31903,8 @@
       <c r="A64" s="44">
         <v>5</v>
       </c>
-      <c r="B64" s="74" t="s">
-        <v>104</v>
+      <c r="B64" s="73" t="s">
+        <v>102</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
@@ -32467,7 +32217,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C65" s="46"/>
       <c r="D65" s="46"/>
@@ -33342,7 +33092,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C66" s="46"/>
       <c r="D66" s="46"/>
@@ -34216,8 +33966,8 @@
       <c r="A67" s="44">
         <v>8</v>
       </c>
-      <c r="B67" s="74" t="s">
-        <v>95</v>
+      <c r="B67" s="73" t="s">
+        <v>93</v>
       </c>
       <c r="C67" s="46"/>
       <c r="D67" s="46"/>
@@ -35091,8 +34841,8 @@
       <c r="A68" s="44">
         <v>9</v>
       </c>
-      <c r="B68" s="74" t="s">
-        <v>96</v>
+      <c r="B68" s="73" t="s">
+        <v>94</v>
       </c>
       <c r="C68" s="46"/>
       <c r="D68" s="46"/>
@@ -35966,8 +35716,8 @@
       <c r="A69" s="44">
         <v>10</v>
       </c>
-      <c r="B69" s="74" t="s">
-        <v>97</v>
+      <c r="B69" s="73" t="s">
+        <v>95</v>
       </c>
       <c r="C69" s="46"/>
       <c r="D69" s="46"/>
@@ -36841,8 +36591,8 @@
       <c r="A70" s="44">
         <v>11</v>
       </c>
-      <c r="B70" s="74" t="s">
-        <v>98</v>
+      <c r="B70" s="73" t="s">
+        <v>96</v>
       </c>
       <c r="C70" s="46"/>
       <c r="D70" s="46"/>
@@ -37714,7 +37464,7 @@
     </row>
     <row r="71" spans="1:307" ht="15.75" customHeight="1">
       <c r="A71" s="49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B71" s="50"/>
       <c r="C71" s="50"/>
@@ -38028,7 +37778,7 @@
         <v>1</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C72" s="53"/>
       <c r="D72" s="53"/>
@@ -38903,7 +38653,7 @@
         <v>2</v>
       </c>
       <c r="B73" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C73" s="53"/>
       <c r="D73" s="53"/>
@@ -39777,8 +39527,8 @@
       <c r="A74" s="51">
         <v>3</v>
       </c>
-      <c r="B74" s="77" t="s">
-        <v>105</v>
+      <c r="B74" s="76" t="s">
+        <v>103</v>
       </c>
       <c r="C74" s="53"/>
       <c r="D74" s="53"/>
@@ -40091,7 +39841,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75" s="53"/>
       <c r="D75" s="53"/>
@@ -40966,7 +40716,7 @@
         <v>5</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C76" s="53"/>
       <c r="D76" s="53"/>
@@ -41838,7 +41588,7 @@
     </row>
     <row r="77" spans="1:307" ht="15.75" customHeight="1">
       <c r="A77" s="56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B77" s="57"/>
       <c r="C77" s="57"/>
@@ -42152,7 +41902,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="60"/>
       <c r="D78" s="60"/>
@@ -43027,7 +42777,7 @@
         <v>2</v>
       </c>
       <c r="B79" s="59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" s="60"/>
       <c r="D79" s="60"/>
@@ -43902,7 +43652,7 @@
         <v>3</v>
       </c>
       <c r="B80" s="59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
@@ -44777,7 +44527,7 @@
         <v>4</v>
       </c>
       <c r="B81" s="59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C81" s="60"/>
       <c r="D81" s="60"/>
@@ -45649,7 +45399,7 @@
     </row>
     <row r="82" spans="1:307" ht="15.75" customHeight="1">
       <c r="A82" s="56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82" s="57"/>
       <c r="C82" s="57"/>
@@ -45963,7 +45713,7 @@
         <v>1</v>
       </c>
       <c r="B83" s="59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="60"/>
       <c r="D83" s="60"/>
@@ -46838,7 +46588,7 @@
         <v>2</v>
       </c>
       <c r="B84" s="59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C84" s="60"/>
       <c r="D84" s="60"/>
@@ -47713,7 +47463,7 @@
         <v>3</v>
       </c>
       <c r="B85" s="59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C85" s="60"/>
       <c r="D85" s="60"/>
@@ -48588,7 +48338,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" s="60"/>
       <c r="D86" s="60"/>
@@ -50071,24 +49821,29 @@
     <mergeCell ref="HJ1:IN1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
-  <conditionalFormatting sqref="A4:KU86">
-    <cfRule type="expression" dxfId="3" priority="2">
+  <conditionalFormatting sqref="A4:KU29 A39:KU86 A30:A38 B30:J30 L30:AV30 B32:KU38 B31:BA31 BC31:KU31 BB30:BB31 BC30 BI30:BJ30 BP30:BQ30 BW30:BX30">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>OR(WEEKDAY(A$2)=1,WEEKDAY(A$2)=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:AH14 AI4:AI25">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>OR(TEXT($AI$2, "ddd")="Sat", TEXT($AI$2, "ddd")="Sun")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U17">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>OR(TEXT($AI$2, "ddd")="Sat", TEXT($AI$2, "ddd")="Sun")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB4:KU86">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="AB4:KU29 AB30:AV30 AB32:KU86 AB31:BA31 BC31:KU31 BI30:BJ30 BP30:BQ30 BW30:BX30">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($F4&lt;&gt;"", $G4&lt;&gt;"", AB$2&gt;=$F4, AB$2&lt;=$G4, WEEKDAY(AB$2,2)&lt;6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB30:BB31 BC30">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>AND($F31&lt;&gt;"", $G31&lt;&gt;"", BB$2&gt;=$F31, BB$2&lt;=$G31, WEEKDAY(BB$2,2)&lt;6)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/【Creepy Code】ガントチャート_PC.xlsx
+++ b/docs/【Creepy Code】ガントチャート_PC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nishi\OneDrive\ドキュメント\Creepy-Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14FA365-2350-4505-BFF3-B2FEA3033C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CF7943-2623-4BFF-848E-E9D40815E3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -960,7 +960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1085,14 +1085,6 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1105,19 +1097,20 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA5A5A5"/>
-          <bgColor rgb="FFA5A5A5"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1153,6 +1146,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFBFBFBF"/>
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA5A5A5"/>
+          <bgColor rgb="FFA5A5A5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1471,297 +1472,297 @@
       <c r="AF1" s="5"/>
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
-      <c r="AI1" s="79" t="s">
+      <c r="AI1" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" s="77"/>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="77"/>
-      <c r="AO1" s="77"/>
-      <c r="AP1" s="77"/>
-      <c r="AQ1" s="77"/>
-      <c r="AR1" s="77"/>
-      <c r="AS1" s="77"/>
-      <c r="AT1" s="77"/>
-      <c r="AU1" s="77"/>
-      <c r="AV1" s="77"/>
-      <c r="AW1" s="77"/>
-      <c r="AX1" s="77"/>
-      <c r="AY1" s="77"/>
-      <c r="AZ1" s="77"/>
-      <c r="BA1" s="77"/>
-      <c r="BB1" s="77"/>
-      <c r="BC1" s="77"/>
-      <c r="BD1" s="77"/>
-      <c r="BE1" s="77"/>
-      <c r="BF1" s="77"/>
-      <c r="BG1" s="77"/>
-      <c r="BH1" s="77"/>
-      <c r="BI1" s="77"/>
-      <c r="BJ1" s="77"/>
-      <c r="BK1" s="77"/>
-      <c r="BL1" s="78"/>
-      <c r="BM1" s="76" t="s">
+      <c r="AJ1" s="83"/>
+      <c r="AK1" s="83"/>
+      <c r="AL1" s="83"/>
+      <c r="AM1" s="83"/>
+      <c r="AN1" s="83"/>
+      <c r="AO1" s="83"/>
+      <c r="AP1" s="83"/>
+      <c r="AQ1" s="83"/>
+      <c r="AR1" s="83"/>
+      <c r="AS1" s="83"/>
+      <c r="AT1" s="83"/>
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="83"/>
+      <c r="AW1" s="83"/>
+      <c r="AX1" s="83"/>
+      <c r="AY1" s="83"/>
+      <c r="AZ1" s="83"/>
+      <c r="BA1" s="83"/>
+      <c r="BB1" s="83"/>
+      <c r="BC1" s="83"/>
+      <c r="BD1" s="83"/>
+      <c r="BE1" s="83"/>
+      <c r="BF1" s="83"/>
+      <c r="BG1" s="83"/>
+      <c r="BH1" s="83"/>
+      <c r="BI1" s="83"/>
+      <c r="BJ1" s="83"/>
+      <c r="BK1" s="83"/>
+      <c r="BL1" s="84"/>
+      <c r="BM1" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="BN1" s="77"/>
-      <c r="BO1" s="77"/>
-      <c r="BP1" s="77"/>
-      <c r="BQ1" s="77"/>
-      <c r="BR1" s="77"/>
-      <c r="BS1" s="77"/>
-      <c r="BT1" s="77"/>
-      <c r="BU1" s="77"/>
-      <c r="BV1" s="77"/>
-      <c r="BW1" s="77"/>
-      <c r="BX1" s="77"/>
-      <c r="BY1" s="77"/>
-      <c r="BZ1" s="77"/>
-      <c r="CA1" s="77"/>
-      <c r="CB1" s="77"/>
-      <c r="CC1" s="77"/>
-      <c r="CD1" s="77"/>
-      <c r="CE1" s="77"/>
-      <c r="CF1" s="77"/>
-      <c r="CG1" s="77"/>
-      <c r="CH1" s="77"/>
-      <c r="CI1" s="77"/>
-      <c r="CJ1" s="77"/>
-      <c r="CK1" s="77"/>
-      <c r="CL1" s="77"/>
-      <c r="CM1" s="77"/>
-      <c r="CN1" s="77"/>
-      <c r="CO1" s="77"/>
-      <c r="CP1" s="77"/>
-      <c r="CQ1" s="78"/>
-      <c r="CR1" s="76" t="s">
+      <c r="BN1" s="83"/>
+      <c r="BO1" s="83"/>
+      <c r="BP1" s="83"/>
+      <c r="BQ1" s="83"/>
+      <c r="BR1" s="83"/>
+      <c r="BS1" s="83"/>
+      <c r="BT1" s="83"/>
+      <c r="BU1" s="83"/>
+      <c r="BV1" s="83"/>
+      <c r="BW1" s="83"/>
+      <c r="BX1" s="83"/>
+      <c r="BY1" s="83"/>
+      <c r="BZ1" s="83"/>
+      <c r="CA1" s="83"/>
+      <c r="CB1" s="83"/>
+      <c r="CC1" s="83"/>
+      <c r="CD1" s="83"/>
+      <c r="CE1" s="83"/>
+      <c r="CF1" s="83"/>
+      <c r="CG1" s="83"/>
+      <c r="CH1" s="83"/>
+      <c r="CI1" s="83"/>
+      <c r="CJ1" s="83"/>
+      <c r="CK1" s="83"/>
+      <c r="CL1" s="83"/>
+      <c r="CM1" s="83"/>
+      <c r="CN1" s="83"/>
+      <c r="CO1" s="83"/>
+      <c r="CP1" s="83"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="CS1" s="77"/>
-      <c r="CT1" s="77"/>
-      <c r="CU1" s="77"/>
-      <c r="CV1" s="77"/>
-      <c r="CW1" s="77"/>
-      <c r="CX1" s="77"/>
-      <c r="CY1" s="77"/>
-      <c r="CZ1" s="77"/>
-      <c r="DA1" s="77"/>
-      <c r="DB1" s="77"/>
-      <c r="DC1" s="77"/>
-      <c r="DD1" s="77"/>
-      <c r="DE1" s="77"/>
-      <c r="DF1" s="77"/>
-      <c r="DG1" s="77"/>
-      <c r="DH1" s="77"/>
-      <c r="DI1" s="77"/>
-      <c r="DJ1" s="77"/>
-      <c r="DK1" s="77"/>
-      <c r="DL1" s="77"/>
-      <c r="DM1" s="77"/>
-      <c r="DN1" s="77"/>
-      <c r="DO1" s="77"/>
-      <c r="DP1" s="77"/>
-      <c r="DQ1" s="77"/>
-      <c r="DR1" s="77"/>
-      <c r="DS1" s="77"/>
-      <c r="DT1" s="77"/>
-      <c r="DU1" s="77"/>
-      <c r="DV1" s="78"/>
-      <c r="DW1" s="76" t="s">
+      <c r="CS1" s="83"/>
+      <c r="CT1" s="83"/>
+      <c r="CU1" s="83"/>
+      <c r="CV1" s="83"/>
+      <c r="CW1" s="83"/>
+      <c r="CX1" s="83"/>
+      <c r="CY1" s="83"/>
+      <c r="CZ1" s="83"/>
+      <c r="DA1" s="83"/>
+      <c r="DB1" s="83"/>
+      <c r="DC1" s="83"/>
+      <c r="DD1" s="83"/>
+      <c r="DE1" s="83"/>
+      <c r="DF1" s="83"/>
+      <c r="DG1" s="83"/>
+      <c r="DH1" s="83"/>
+      <c r="DI1" s="83"/>
+      <c r="DJ1" s="83"/>
+      <c r="DK1" s="83"/>
+      <c r="DL1" s="83"/>
+      <c r="DM1" s="83"/>
+      <c r="DN1" s="83"/>
+      <c r="DO1" s="83"/>
+      <c r="DP1" s="83"/>
+      <c r="DQ1" s="83"/>
+      <c r="DR1" s="83"/>
+      <c r="DS1" s="83"/>
+      <c r="DT1" s="83"/>
+      <c r="DU1" s="83"/>
+      <c r="DV1" s="84"/>
+      <c r="DW1" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="DX1" s="77"/>
-      <c r="DY1" s="77"/>
-      <c r="DZ1" s="77"/>
-      <c r="EA1" s="77"/>
-      <c r="EB1" s="77"/>
-      <c r="EC1" s="77"/>
-      <c r="ED1" s="77"/>
-      <c r="EE1" s="77"/>
-      <c r="EF1" s="77"/>
-      <c r="EG1" s="77"/>
-      <c r="EH1" s="77"/>
-      <c r="EI1" s="77"/>
-      <c r="EJ1" s="77"/>
-      <c r="EK1" s="77"/>
-      <c r="EL1" s="77"/>
-      <c r="EM1" s="77"/>
-      <c r="EN1" s="77"/>
-      <c r="EO1" s="77"/>
-      <c r="EP1" s="77"/>
-      <c r="EQ1" s="77"/>
-      <c r="ER1" s="77"/>
-      <c r="ES1" s="77"/>
-      <c r="ET1" s="77"/>
-      <c r="EU1" s="77"/>
-      <c r="EV1" s="77"/>
-      <c r="EW1" s="77"/>
-      <c r="EX1" s="77"/>
-      <c r="EY1" s="77"/>
-      <c r="EZ1" s="77"/>
-      <c r="FA1" s="76" t="s">
+      <c r="DX1" s="83"/>
+      <c r="DY1" s="83"/>
+      <c r="DZ1" s="83"/>
+      <c r="EA1" s="83"/>
+      <c r="EB1" s="83"/>
+      <c r="EC1" s="83"/>
+      <c r="ED1" s="83"/>
+      <c r="EE1" s="83"/>
+      <c r="EF1" s="83"/>
+      <c r="EG1" s="83"/>
+      <c r="EH1" s="83"/>
+      <c r="EI1" s="83"/>
+      <c r="EJ1" s="83"/>
+      <c r="EK1" s="83"/>
+      <c r="EL1" s="83"/>
+      <c r="EM1" s="83"/>
+      <c r="EN1" s="83"/>
+      <c r="EO1" s="83"/>
+      <c r="EP1" s="83"/>
+      <c r="EQ1" s="83"/>
+      <c r="ER1" s="83"/>
+      <c r="ES1" s="83"/>
+      <c r="ET1" s="83"/>
+      <c r="EU1" s="83"/>
+      <c r="EV1" s="83"/>
+      <c r="EW1" s="83"/>
+      <c r="EX1" s="83"/>
+      <c r="EY1" s="83"/>
+      <c r="EZ1" s="83"/>
+      <c r="FA1" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="FB1" s="77"/>
-      <c r="FC1" s="77"/>
-      <c r="FD1" s="77"/>
-      <c r="FE1" s="77"/>
-      <c r="FF1" s="77"/>
-      <c r="FG1" s="77"/>
-      <c r="FH1" s="77"/>
-      <c r="FI1" s="77"/>
-      <c r="FJ1" s="77"/>
-      <c r="FK1" s="77"/>
-      <c r="FL1" s="77"/>
-      <c r="FM1" s="77"/>
-      <c r="FN1" s="77"/>
-      <c r="FO1" s="77"/>
-      <c r="FP1" s="77"/>
-      <c r="FQ1" s="77"/>
-      <c r="FR1" s="77"/>
-      <c r="FS1" s="77"/>
-      <c r="FT1" s="77"/>
-      <c r="FU1" s="77"/>
-      <c r="FV1" s="77"/>
-      <c r="FW1" s="77"/>
-      <c r="FX1" s="77"/>
-      <c r="FY1" s="77"/>
-      <c r="FZ1" s="77"/>
-      <c r="GA1" s="77"/>
-      <c r="GB1" s="77"/>
-      <c r="GC1" s="77"/>
-      <c r="GD1" s="77"/>
-      <c r="GE1" s="78"/>
-      <c r="GF1" s="76" t="s">
+      <c r="FB1" s="83"/>
+      <c r="FC1" s="83"/>
+      <c r="FD1" s="83"/>
+      <c r="FE1" s="83"/>
+      <c r="FF1" s="83"/>
+      <c r="FG1" s="83"/>
+      <c r="FH1" s="83"/>
+      <c r="FI1" s="83"/>
+      <c r="FJ1" s="83"/>
+      <c r="FK1" s="83"/>
+      <c r="FL1" s="83"/>
+      <c r="FM1" s="83"/>
+      <c r="FN1" s="83"/>
+      <c r="FO1" s="83"/>
+      <c r="FP1" s="83"/>
+      <c r="FQ1" s="83"/>
+      <c r="FR1" s="83"/>
+      <c r="FS1" s="83"/>
+      <c r="FT1" s="83"/>
+      <c r="FU1" s="83"/>
+      <c r="FV1" s="83"/>
+      <c r="FW1" s="83"/>
+      <c r="FX1" s="83"/>
+      <c r="FY1" s="83"/>
+      <c r="FZ1" s="83"/>
+      <c r="GA1" s="83"/>
+      <c r="GB1" s="83"/>
+      <c r="GC1" s="83"/>
+      <c r="GD1" s="83"/>
+      <c r="GE1" s="84"/>
+      <c r="GF1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="GG1" s="77"/>
-      <c r="GH1" s="77"/>
-      <c r="GI1" s="77"/>
-      <c r="GJ1" s="77"/>
-      <c r="GK1" s="77"/>
-      <c r="GL1" s="77"/>
-      <c r="GM1" s="77"/>
-      <c r="GN1" s="77"/>
-      <c r="GO1" s="77"/>
-      <c r="GP1" s="77"/>
-      <c r="GQ1" s="77"/>
-      <c r="GR1" s="77"/>
-      <c r="GS1" s="77"/>
-      <c r="GT1" s="77"/>
-      <c r="GU1" s="77"/>
-      <c r="GV1" s="77"/>
-      <c r="GW1" s="77"/>
-      <c r="GX1" s="77"/>
-      <c r="GY1" s="77"/>
-      <c r="GZ1" s="77"/>
-      <c r="HA1" s="77"/>
-      <c r="HB1" s="77"/>
-      <c r="HC1" s="77"/>
-      <c r="HD1" s="77"/>
-      <c r="HE1" s="77"/>
-      <c r="HF1" s="77"/>
-      <c r="HG1" s="77"/>
-      <c r="HH1" s="77"/>
-      <c r="HI1" s="77"/>
-      <c r="HJ1" s="76" t="s">
+      <c r="GG1" s="83"/>
+      <c r="GH1" s="83"/>
+      <c r="GI1" s="83"/>
+      <c r="GJ1" s="83"/>
+      <c r="GK1" s="83"/>
+      <c r="GL1" s="83"/>
+      <c r="GM1" s="83"/>
+      <c r="GN1" s="83"/>
+      <c r="GO1" s="83"/>
+      <c r="GP1" s="83"/>
+      <c r="GQ1" s="83"/>
+      <c r="GR1" s="83"/>
+      <c r="GS1" s="83"/>
+      <c r="GT1" s="83"/>
+      <c r="GU1" s="83"/>
+      <c r="GV1" s="83"/>
+      <c r="GW1" s="83"/>
+      <c r="GX1" s="83"/>
+      <c r="GY1" s="83"/>
+      <c r="GZ1" s="83"/>
+      <c r="HA1" s="83"/>
+      <c r="HB1" s="83"/>
+      <c r="HC1" s="83"/>
+      <c r="HD1" s="83"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="83"/>
+      <c r="HG1" s="83"/>
+      <c r="HH1" s="83"/>
+      <c r="HI1" s="83"/>
+      <c r="HJ1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="HK1" s="77"/>
-      <c r="HL1" s="77"/>
-      <c r="HM1" s="77"/>
-      <c r="HN1" s="77"/>
-      <c r="HO1" s="77"/>
-      <c r="HP1" s="77"/>
-      <c r="HQ1" s="77"/>
-      <c r="HR1" s="77"/>
-      <c r="HS1" s="77"/>
-      <c r="HT1" s="77"/>
-      <c r="HU1" s="77"/>
-      <c r="HV1" s="77"/>
-      <c r="HW1" s="77"/>
-      <c r="HX1" s="77"/>
-      <c r="HY1" s="77"/>
-      <c r="HZ1" s="77"/>
-      <c r="IA1" s="77"/>
-      <c r="IB1" s="77"/>
-      <c r="IC1" s="77"/>
-      <c r="ID1" s="77"/>
-      <c r="IE1" s="77"/>
-      <c r="IF1" s="77"/>
-      <c r="IG1" s="77"/>
-      <c r="IH1" s="77"/>
-      <c r="II1" s="77"/>
-      <c r="IJ1" s="77"/>
-      <c r="IK1" s="77"/>
-      <c r="IL1" s="77"/>
-      <c r="IM1" s="77"/>
-      <c r="IN1" s="78"/>
-      <c r="IO1" s="76" t="s">
+      <c r="HK1" s="83"/>
+      <c r="HL1" s="83"/>
+      <c r="HM1" s="83"/>
+      <c r="HN1" s="83"/>
+      <c r="HO1" s="83"/>
+      <c r="HP1" s="83"/>
+      <c r="HQ1" s="83"/>
+      <c r="HR1" s="83"/>
+      <c r="HS1" s="83"/>
+      <c r="HT1" s="83"/>
+      <c r="HU1" s="83"/>
+      <c r="HV1" s="83"/>
+      <c r="HW1" s="83"/>
+      <c r="HX1" s="83"/>
+      <c r="HY1" s="83"/>
+      <c r="HZ1" s="83"/>
+      <c r="IA1" s="83"/>
+      <c r="IB1" s="83"/>
+      <c r="IC1" s="83"/>
+      <c r="ID1" s="83"/>
+      <c r="IE1" s="83"/>
+      <c r="IF1" s="83"/>
+      <c r="IG1" s="83"/>
+      <c r="IH1" s="83"/>
+      <c r="II1" s="83"/>
+      <c r="IJ1" s="83"/>
+      <c r="IK1" s="83"/>
+      <c r="IL1" s="83"/>
+      <c r="IM1" s="83"/>
+      <c r="IN1" s="84"/>
+      <c r="IO1" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="IP1" s="77"/>
-      <c r="IQ1" s="77"/>
-      <c r="IR1" s="77"/>
-      <c r="IS1" s="77"/>
-      <c r="IT1" s="77"/>
-      <c r="IU1" s="77"/>
-      <c r="IV1" s="77"/>
-      <c r="IW1" s="77"/>
-      <c r="IX1" s="77"/>
-      <c r="IY1" s="77"/>
-      <c r="IZ1" s="77"/>
-      <c r="JA1" s="77"/>
-      <c r="JB1" s="77"/>
-      <c r="JC1" s="77"/>
-      <c r="JD1" s="77"/>
-      <c r="JE1" s="77"/>
-      <c r="JF1" s="77"/>
-      <c r="JG1" s="77"/>
-      <c r="JH1" s="77"/>
-      <c r="JI1" s="77"/>
-      <c r="JJ1" s="77"/>
-      <c r="JK1" s="77"/>
-      <c r="JL1" s="77"/>
-      <c r="JM1" s="77"/>
-      <c r="JN1" s="77"/>
-      <c r="JO1" s="77"/>
-      <c r="JP1" s="77"/>
-      <c r="JQ1" s="77"/>
-      <c r="JR1" s="77"/>
-      <c r="JS1" s="78"/>
-      <c r="JT1" s="76" t="s">
+      <c r="IP1" s="83"/>
+      <c r="IQ1" s="83"/>
+      <c r="IR1" s="83"/>
+      <c r="IS1" s="83"/>
+      <c r="IT1" s="83"/>
+      <c r="IU1" s="83"/>
+      <c r="IV1" s="83"/>
+      <c r="IW1" s="83"/>
+      <c r="IX1" s="83"/>
+      <c r="IY1" s="83"/>
+      <c r="IZ1" s="83"/>
+      <c r="JA1" s="83"/>
+      <c r="JB1" s="83"/>
+      <c r="JC1" s="83"/>
+      <c r="JD1" s="83"/>
+      <c r="JE1" s="83"/>
+      <c r="JF1" s="83"/>
+      <c r="JG1" s="83"/>
+      <c r="JH1" s="83"/>
+      <c r="JI1" s="83"/>
+      <c r="JJ1" s="83"/>
+      <c r="JK1" s="83"/>
+      <c r="JL1" s="83"/>
+      <c r="JM1" s="83"/>
+      <c r="JN1" s="83"/>
+      <c r="JO1" s="83"/>
+      <c r="JP1" s="83"/>
+      <c r="JQ1" s="83"/>
+      <c r="JR1" s="83"/>
+      <c r="JS1" s="84"/>
+      <c r="JT1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="JU1" s="77"/>
-      <c r="JV1" s="77"/>
-      <c r="JW1" s="77"/>
-      <c r="JX1" s="77"/>
-      <c r="JY1" s="77"/>
-      <c r="JZ1" s="77"/>
-      <c r="KA1" s="77"/>
-      <c r="KB1" s="77"/>
-      <c r="KC1" s="77"/>
-      <c r="KD1" s="77"/>
-      <c r="KE1" s="77"/>
-      <c r="KF1" s="77"/>
-      <c r="KG1" s="77"/>
-      <c r="KH1" s="77"/>
-      <c r="KI1" s="77"/>
-      <c r="KJ1" s="77"/>
-      <c r="KK1" s="77"/>
-      <c r="KL1" s="77"/>
-      <c r="KM1" s="77"/>
-      <c r="KN1" s="77"/>
-      <c r="KO1" s="77"/>
-      <c r="KP1" s="77"/>
-      <c r="KQ1" s="77"/>
-      <c r="KR1" s="77"/>
-      <c r="KS1" s="77"/>
-      <c r="KT1" s="77"/>
-      <c r="KU1" s="77"/>
+      <c r="JU1" s="83"/>
+      <c r="JV1" s="83"/>
+      <c r="JW1" s="83"/>
+      <c r="JX1" s="83"/>
+      <c r="JY1" s="83"/>
+      <c r="JZ1" s="83"/>
+      <c r="KA1" s="83"/>
+      <c r="KB1" s="83"/>
+      <c r="KC1" s="83"/>
+      <c r="KD1" s="83"/>
+      <c r="KE1" s="83"/>
+      <c r="KF1" s="83"/>
+      <c r="KG1" s="83"/>
+      <c r="KH1" s="83"/>
+      <c r="KI1" s="83"/>
+      <c r="KJ1" s="83"/>
+      <c r="KK1" s="83"/>
+      <c r="KL1" s="83"/>
+      <c r="KM1" s="83"/>
+      <c r="KN1" s="83"/>
+      <c r="KO1" s="83"/>
+      <c r="KP1" s="83"/>
+      <c r="KQ1" s="83"/>
+      <c r="KR1" s="83"/>
+      <c r="KS1" s="83"/>
+      <c r="KT1" s="83"/>
+      <c r="KU1" s="83"/>
     </row>
     <row r="2" spans="1:307" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -14291,7 +14292,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="29"/>
-      <c r="D36" s="80" t="s">
+      <c r="D36" s="76" t="s">
         <v>108</v>
       </c>
       <c r="E36" s="29"/>
@@ -14937,11 +14938,11 @@
       <c r="A38" s="27">
         <v>12</v>
       </c>
-      <c r="B38" s="85" t="s">
+      <c r="B38" s="81" t="s">
         <v>109</v>
       </c>
       <c r="C38" s="27"/>
-      <c r="D38" s="83" t="s">
+      <c r="D38" s="79" t="s">
         <v>110</v>
       </c>
       <c r="E38" s="27"/>
@@ -14949,10 +14950,10 @@
         <v>46219</v>
       </c>
       <c r="G38" s="27"/>
-      <c r="H38" s="84">
+      <c r="H38" s="80">
         <v>0.8</v>
       </c>
-      <c r="I38" s="81"/>
+      <c r="I38" s="77"/>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
@@ -14995,11 +14996,11 @@
       <c r="AW38" s="18"/>
       <c r="AX38" s="18"/>
       <c r="AY38" s="18"/>
-      <c r="AZ38" s="82"/>
-      <c r="BA38" s="82"/>
-      <c r="BB38" s="82"/>
-      <c r="BC38" s="82"/>
-      <c r="BD38" s="82"/>
+      <c r="AZ38" s="78"/>
+      <c r="BA38" s="78"/>
+      <c r="BB38" s="78"/>
+      <c r="BC38" s="78"/>
+      <c r="BD38" s="78"/>
       <c r="BE38" s="18"/>
       <c r="BF38" s="18"/>
       <c r="BG38" s="18"/>
@@ -43815,8 +43816,12 @@
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
       <c r="E80" s="60"/>
-      <c r="F80" s="60"/>
-      <c r="G80" s="60"/>
+      <c r="F80" s="86">
+        <v>46351</v>
+      </c>
+      <c r="G80" s="86">
+        <v>46351</v>
+      </c>
       <c r="H80" s="61">
         <v>0</v>
       </c>
@@ -49104,28 +49109,28 @@
     <mergeCell ref="HJ1:IN1"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
-  <conditionalFormatting sqref="L30:AV30 BI30:BJ30 BP30:BQ30 B31:BA31 BC31:KU31 BC30 BB30:BB31 B29:KU29 A4:KU28 BW30:FR30 A39:KU85 B30:J30 A29:A38 B32:KU38">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="A4:KU28 B29:KU29 L30:AV30 BI30:BJ30 BP30:BQ30 BW30:FR30 B31:BA31 BC31:KU31 B32:KU38 A29:A38 B30:J30 BC30 BB30:BB31 A39:KU85">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>OR(WEEKDAY(A$2)=1,WEEKDAY(A$2)=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:AH14 AI4:AI25">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>OR(TEXT($AI$2, "ddd")="Sat", TEXT($AI$2, "ddd")="Sun")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U17">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>OR(TEXT($AI$2, "ddd")="Sat", TEXT($AI$2, "ddd")="Sun")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB4:KU29 AB30:AV30 BI30:BJ30 BP30:BQ30 AB31:BA31 BC31:KU31 BW30:FR30 AB32:KU85">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="AB4:KU29 AB30:AV30 BI30:BJ30 BP30:BQ30 BW30:FR30 AB31:BA31 BC31:KU31 AB32:KU85">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($F4&lt;&gt;"", $G4&lt;&gt;"", AB$2&gt;=$F4, AB$2&lt;=$G4, WEEKDAY(AB$2,2)&lt;6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC30 BB30:BB31">
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>AND($F31&lt;&gt;"", $G31&lt;&gt;"", BB$2&gt;=$F31, BB$2&lt;=$G31, WEEKDAY(BB$2,2)&lt;6)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/【Creepy Code】ガントチャート_PC.xlsx
+++ b/docs/【Creepy Code】ガントチャート_PC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nishi\OneDrive\ドキュメント\Creepy-Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CF7943-2623-4BFF-848E-E9D40815E3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90880DD5-45E1-4584-B443-3529BD37AABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1097,6 +1097,7 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1105,7 +1106,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1472,297 +1472,297 @@
       <c r="AF1" s="5"/>
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
-      <c r="AI1" s="85" t="s">
+      <c r="AI1" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" s="83"/>
-      <c r="AK1" s="83"/>
-      <c r="AL1" s="83"/>
-      <c r="AM1" s="83"/>
-      <c r="AN1" s="83"/>
-      <c r="AO1" s="83"/>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AS1" s="83"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AX1" s="83"/>
-      <c r="AY1" s="83"/>
-      <c r="AZ1" s="83"/>
-      <c r="BA1" s="83"/>
-      <c r="BB1" s="83"/>
-      <c r="BC1" s="83"/>
-      <c r="BD1" s="83"/>
-      <c r="BE1" s="83"/>
-      <c r="BF1" s="83"/>
-      <c r="BG1" s="83"/>
-      <c r="BH1" s="83"/>
-      <c r="BI1" s="83"/>
-      <c r="BJ1" s="83"/>
-      <c r="BK1" s="83"/>
-      <c r="BL1" s="84"/>
-      <c r="BM1" s="82" t="s">
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
+      <c r="AM1" s="84"/>
+      <c r="AN1" s="84"/>
+      <c r="AO1" s="84"/>
+      <c r="AP1" s="84"/>
+      <c r="AQ1" s="84"/>
+      <c r="AR1" s="84"/>
+      <c r="AS1" s="84"/>
+      <c r="AT1" s="84"/>
+      <c r="AU1" s="84"/>
+      <c r="AV1" s="84"/>
+      <c r="AW1" s="84"/>
+      <c r="AX1" s="84"/>
+      <c r="AY1" s="84"/>
+      <c r="AZ1" s="84"/>
+      <c r="BA1" s="84"/>
+      <c r="BB1" s="84"/>
+      <c r="BC1" s="84"/>
+      <c r="BD1" s="84"/>
+      <c r="BE1" s="84"/>
+      <c r="BF1" s="84"/>
+      <c r="BG1" s="84"/>
+      <c r="BH1" s="84"/>
+      <c r="BI1" s="84"/>
+      <c r="BJ1" s="84"/>
+      <c r="BK1" s="84"/>
+      <c r="BL1" s="85"/>
+      <c r="BM1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="BN1" s="83"/>
-      <c r="BO1" s="83"/>
-      <c r="BP1" s="83"/>
-      <c r="BQ1" s="83"/>
-      <c r="BR1" s="83"/>
-      <c r="BS1" s="83"/>
-      <c r="BT1" s="83"/>
-      <c r="BU1" s="83"/>
-      <c r="BV1" s="83"/>
-      <c r="BW1" s="83"/>
-      <c r="BX1" s="83"/>
-      <c r="BY1" s="83"/>
-      <c r="BZ1" s="83"/>
-      <c r="CA1" s="83"/>
-      <c r="CB1" s="83"/>
-      <c r="CC1" s="83"/>
-      <c r="CD1" s="83"/>
-      <c r="CE1" s="83"/>
-      <c r="CF1" s="83"/>
-      <c r="CG1" s="83"/>
-      <c r="CH1" s="83"/>
-      <c r="CI1" s="83"/>
-      <c r="CJ1" s="83"/>
-      <c r="CK1" s="83"/>
-      <c r="CL1" s="83"/>
-      <c r="CM1" s="83"/>
-      <c r="CN1" s="83"/>
-      <c r="CO1" s="83"/>
-      <c r="CP1" s="83"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="82" t="s">
+      <c r="BN1" s="84"/>
+      <c r="BO1" s="84"/>
+      <c r="BP1" s="84"/>
+      <c r="BQ1" s="84"/>
+      <c r="BR1" s="84"/>
+      <c r="BS1" s="84"/>
+      <c r="BT1" s="84"/>
+      <c r="BU1" s="84"/>
+      <c r="BV1" s="84"/>
+      <c r="BW1" s="84"/>
+      <c r="BX1" s="84"/>
+      <c r="BY1" s="84"/>
+      <c r="BZ1" s="84"/>
+      <c r="CA1" s="84"/>
+      <c r="CB1" s="84"/>
+      <c r="CC1" s="84"/>
+      <c r="CD1" s="84"/>
+      <c r="CE1" s="84"/>
+      <c r="CF1" s="84"/>
+      <c r="CG1" s="84"/>
+      <c r="CH1" s="84"/>
+      <c r="CI1" s="84"/>
+      <c r="CJ1" s="84"/>
+      <c r="CK1" s="84"/>
+      <c r="CL1" s="84"/>
+      <c r="CM1" s="84"/>
+      <c r="CN1" s="84"/>
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="85"/>
+      <c r="CR1" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="CS1" s="83"/>
-      <c r="CT1" s="83"/>
-      <c r="CU1" s="83"/>
-      <c r="CV1" s="83"/>
-      <c r="CW1" s="83"/>
-      <c r="CX1" s="83"/>
-      <c r="CY1" s="83"/>
-      <c r="CZ1" s="83"/>
-      <c r="DA1" s="83"/>
-      <c r="DB1" s="83"/>
-      <c r="DC1" s="83"/>
-      <c r="DD1" s="83"/>
-      <c r="DE1" s="83"/>
-      <c r="DF1" s="83"/>
-      <c r="DG1" s="83"/>
-      <c r="DH1" s="83"/>
-      <c r="DI1" s="83"/>
-      <c r="DJ1" s="83"/>
-      <c r="DK1" s="83"/>
-      <c r="DL1" s="83"/>
-      <c r="DM1" s="83"/>
-      <c r="DN1" s="83"/>
-      <c r="DO1" s="83"/>
-      <c r="DP1" s="83"/>
-      <c r="DQ1" s="83"/>
-      <c r="DR1" s="83"/>
-      <c r="DS1" s="83"/>
-      <c r="DT1" s="83"/>
-      <c r="DU1" s="83"/>
-      <c r="DV1" s="84"/>
-      <c r="DW1" s="82" t="s">
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="84"/>
+      <c r="DR1" s="84"/>
+      <c r="DS1" s="84"/>
+      <c r="DT1" s="84"/>
+      <c r="DU1" s="84"/>
+      <c r="DV1" s="85"/>
+      <c r="DW1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="DX1" s="83"/>
-      <c r="DY1" s="83"/>
-      <c r="DZ1" s="83"/>
-      <c r="EA1" s="83"/>
-      <c r="EB1" s="83"/>
-      <c r="EC1" s="83"/>
-      <c r="ED1" s="83"/>
-      <c r="EE1" s="83"/>
-      <c r="EF1" s="83"/>
-      <c r="EG1" s="83"/>
-      <c r="EH1" s="83"/>
-      <c r="EI1" s="83"/>
-      <c r="EJ1" s="83"/>
-      <c r="EK1" s="83"/>
-      <c r="EL1" s="83"/>
-      <c r="EM1" s="83"/>
-      <c r="EN1" s="83"/>
-      <c r="EO1" s="83"/>
-      <c r="EP1" s="83"/>
-      <c r="EQ1" s="83"/>
-      <c r="ER1" s="83"/>
-      <c r="ES1" s="83"/>
-      <c r="ET1" s="83"/>
-      <c r="EU1" s="83"/>
-      <c r="EV1" s="83"/>
-      <c r="EW1" s="83"/>
-      <c r="EX1" s="83"/>
-      <c r="EY1" s="83"/>
-      <c r="EZ1" s="83"/>
-      <c r="FA1" s="82" t="s">
+      <c r="DX1" s="84"/>
+      <c r="DY1" s="84"/>
+      <c r="DZ1" s="84"/>
+      <c r="EA1" s="84"/>
+      <c r="EB1" s="84"/>
+      <c r="EC1" s="84"/>
+      <c r="ED1" s="84"/>
+      <c r="EE1" s="84"/>
+      <c r="EF1" s="84"/>
+      <c r="EG1" s="84"/>
+      <c r="EH1" s="84"/>
+      <c r="EI1" s="84"/>
+      <c r="EJ1" s="84"/>
+      <c r="EK1" s="84"/>
+      <c r="EL1" s="84"/>
+      <c r="EM1" s="84"/>
+      <c r="EN1" s="84"/>
+      <c r="EO1" s="84"/>
+      <c r="EP1" s="84"/>
+      <c r="EQ1" s="84"/>
+      <c r="ER1" s="84"/>
+      <c r="ES1" s="84"/>
+      <c r="ET1" s="84"/>
+      <c r="EU1" s="84"/>
+      <c r="EV1" s="84"/>
+      <c r="EW1" s="84"/>
+      <c r="EX1" s="84"/>
+      <c r="EY1" s="84"/>
+      <c r="EZ1" s="84"/>
+      <c r="FA1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="FB1" s="83"/>
-      <c r="FC1" s="83"/>
-      <c r="FD1" s="83"/>
-      <c r="FE1" s="83"/>
-      <c r="FF1" s="83"/>
-      <c r="FG1" s="83"/>
-      <c r="FH1" s="83"/>
-      <c r="FI1" s="83"/>
-      <c r="FJ1" s="83"/>
-      <c r="FK1" s="83"/>
-      <c r="FL1" s="83"/>
-      <c r="FM1" s="83"/>
-      <c r="FN1" s="83"/>
-      <c r="FO1" s="83"/>
-      <c r="FP1" s="83"/>
-      <c r="FQ1" s="83"/>
-      <c r="FR1" s="83"/>
-      <c r="FS1" s="83"/>
-      <c r="FT1" s="83"/>
-      <c r="FU1" s="83"/>
-      <c r="FV1" s="83"/>
-      <c r="FW1" s="83"/>
-      <c r="FX1" s="83"/>
-      <c r="FY1" s="83"/>
-      <c r="FZ1" s="83"/>
-      <c r="GA1" s="83"/>
-      <c r="GB1" s="83"/>
-      <c r="GC1" s="83"/>
-      <c r="GD1" s="83"/>
-      <c r="GE1" s="84"/>
-      <c r="GF1" s="82" t="s">
+      <c r="FB1" s="84"/>
+      <c r="FC1" s="84"/>
+      <c r="FD1" s="84"/>
+      <c r="FE1" s="84"/>
+      <c r="FF1" s="84"/>
+      <c r="FG1" s="84"/>
+      <c r="FH1" s="84"/>
+      <c r="FI1" s="84"/>
+      <c r="FJ1" s="84"/>
+      <c r="FK1" s="84"/>
+      <c r="FL1" s="84"/>
+      <c r="FM1" s="84"/>
+      <c r="FN1" s="84"/>
+      <c r="FO1" s="84"/>
+      <c r="FP1" s="84"/>
+      <c r="FQ1" s="84"/>
+      <c r="FR1" s="84"/>
+      <c r="FS1" s="84"/>
+      <c r="FT1" s="84"/>
+      <c r="FU1" s="84"/>
+      <c r="FV1" s="84"/>
+      <c r="FW1" s="84"/>
+      <c r="FX1" s="84"/>
+      <c r="FY1" s="84"/>
+      <c r="FZ1" s="84"/>
+      <c r="GA1" s="84"/>
+      <c r="GB1" s="84"/>
+      <c r="GC1" s="84"/>
+      <c r="GD1" s="84"/>
+      <c r="GE1" s="85"/>
+      <c r="GF1" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="GG1" s="83"/>
-      <c r="GH1" s="83"/>
-      <c r="GI1" s="83"/>
-      <c r="GJ1" s="83"/>
-      <c r="GK1" s="83"/>
-      <c r="GL1" s="83"/>
-      <c r="GM1" s="83"/>
-      <c r="GN1" s="83"/>
-      <c r="GO1" s="83"/>
-      <c r="GP1" s="83"/>
-      <c r="GQ1" s="83"/>
-      <c r="GR1" s="83"/>
-      <c r="GS1" s="83"/>
-      <c r="GT1" s="83"/>
-      <c r="GU1" s="83"/>
-      <c r="GV1" s="83"/>
-      <c r="GW1" s="83"/>
-      <c r="GX1" s="83"/>
-      <c r="GY1" s="83"/>
-      <c r="GZ1" s="83"/>
-      <c r="HA1" s="83"/>
-      <c r="HB1" s="83"/>
-      <c r="HC1" s="83"/>
-      <c r="HD1" s="83"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="83"/>
-      <c r="HG1" s="83"/>
-      <c r="HH1" s="83"/>
-      <c r="HI1" s="83"/>
-      <c r="HJ1" s="82" t="s">
+      <c r="GG1" s="84"/>
+      <c r="GH1" s="84"/>
+      <c r="GI1" s="84"/>
+      <c r="GJ1" s="84"/>
+      <c r="GK1" s="84"/>
+      <c r="GL1" s="84"/>
+      <c r="GM1" s="84"/>
+      <c r="GN1" s="84"/>
+      <c r="GO1" s="84"/>
+      <c r="GP1" s="84"/>
+      <c r="GQ1" s="84"/>
+      <c r="GR1" s="84"/>
+      <c r="GS1" s="84"/>
+      <c r="GT1" s="84"/>
+      <c r="GU1" s="84"/>
+      <c r="GV1" s="84"/>
+      <c r="GW1" s="84"/>
+      <c r="GX1" s="84"/>
+      <c r="GY1" s="84"/>
+      <c r="GZ1" s="84"/>
+      <c r="HA1" s="84"/>
+      <c r="HB1" s="84"/>
+      <c r="HC1" s="84"/>
+      <c r="HD1" s="84"/>
+      <c r="HE1" s="84"/>
+      <c r="HF1" s="84"/>
+      <c r="HG1" s="84"/>
+      <c r="HH1" s="84"/>
+      <c r="HI1" s="84"/>
+      <c r="HJ1" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="HK1" s="83"/>
-      <c r="HL1" s="83"/>
-      <c r="HM1" s="83"/>
-      <c r="HN1" s="83"/>
-      <c r="HO1" s="83"/>
-      <c r="HP1" s="83"/>
-      <c r="HQ1" s="83"/>
-      <c r="HR1" s="83"/>
-      <c r="HS1" s="83"/>
-      <c r="HT1" s="83"/>
-      <c r="HU1" s="83"/>
-      <c r="HV1" s="83"/>
-      <c r="HW1" s="83"/>
-      <c r="HX1" s="83"/>
-      <c r="HY1" s="83"/>
-      <c r="HZ1" s="83"/>
-      <c r="IA1" s="83"/>
-      <c r="IB1" s="83"/>
-      <c r="IC1" s="83"/>
-      <c r="ID1" s="83"/>
-      <c r="IE1" s="83"/>
-      <c r="IF1" s="83"/>
-      <c r="IG1" s="83"/>
-      <c r="IH1" s="83"/>
-      <c r="II1" s="83"/>
-      <c r="IJ1" s="83"/>
-      <c r="IK1" s="83"/>
-      <c r="IL1" s="83"/>
-      <c r="IM1" s="83"/>
-      <c r="IN1" s="84"/>
-      <c r="IO1" s="82" t="s">
+      <c r="HK1" s="84"/>
+      <c r="HL1" s="84"/>
+      <c r="HM1" s="84"/>
+      <c r="HN1" s="84"/>
+      <c r="HO1" s="84"/>
+      <c r="HP1" s="84"/>
+      <c r="HQ1" s="84"/>
+      <c r="HR1" s="84"/>
+      <c r="HS1" s="84"/>
+      <c r="HT1" s="84"/>
+      <c r="HU1" s="84"/>
+      <c r="HV1" s="84"/>
+      <c r="HW1" s="84"/>
+      <c r="HX1" s="84"/>
+      <c r="HY1" s="84"/>
+      <c r="HZ1" s="84"/>
+      <c r="IA1" s="84"/>
+      <c r="IB1" s="84"/>
+      <c r="IC1" s="84"/>
+      <c r="ID1" s="84"/>
+      <c r="IE1" s="84"/>
+      <c r="IF1" s="84"/>
+      <c r="IG1" s="84"/>
+      <c r="IH1" s="84"/>
+      <c r="II1" s="84"/>
+      <c r="IJ1" s="84"/>
+      <c r="IK1" s="84"/>
+      <c r="IL1" s="84"/>
+      <c r="IM1" s="84"/>
+      <c r="IN1" s="85"/>
+      <c r="IO1" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="IP1" s="83"/>
-      <c r="IQ1" s="83"/>
-      <c r="IR1" s="83"/>
-      <c r="IS1" s="83"/>
-      <c r="IT1" s="83"/>
-      <c r="IU1" s="83"/>
-      <c r="IV1" s="83"/>
-      <c r="IW1" s="83"/>
-      <c r="IX1" s="83"/>
-      <c r="IY1" s="83"/>
-      <c r="IZ1" s="83"/>
-      <c r="JA1" s="83"/>
-      <c r="JB1" s="83"/>
-      <c r="JC1" s="83"/>
-      <c r="JD1" s="83"/>
-      <c r="JE1" s="83"/>
-      <c r="JF1" s="83"/>
-      <c r="JG1" s="83"/>
-      <c r="JH1" s="83"/>
-      <c r="JI1" s="83"/>
-      <c r="JJ1" s="83"/>
-      <c r="JK1" s="83"/>
-      <c r="JL1" s="83"/>
-      <c r="JM1" s="83"/>
-      <c r="JN1" s="83"/>
-      <c r="JO1" s="83"/>
-      <c r="JP1" s="83"/>
-      <c r="JQ1" s="83"/>
-      <c r="JR1" s="83"/>
-      <c r="JS1" s="84"/>
-      <c r="JT1" s="82" t="s">
+      <c r="IP1" s="84"/>
+      <c r="IQ1" s="84"/>
+      <c r="IR1" s="84"/>
+      <c r="IS1" s="84"/>
+      <c r="IT1" s="84"/>
+      <c r="IU1" s="84"/>
+      <c r="IV1" s="84"/>
+      <c r="IW1" s="84"/>
+      <c r="IX1" s="84"/>
+      <c r="IY1" s="84"/>
+      <c r="IZ1" s="84"/>
+      <c r="JA1" s="84"/>
+      <c r="JB1" s="84"/>
+      <c r="JC1" s="84"/>
+      <c r="JD1" s="84"/>
+      <c r="JE1" s="84"/>
+      <c r="JF1" s="84"/>
+      <c r="JG1" s="84"/>
+      <c r="JH1" s="84"/>
+      <c r="JI1" s="84"/>
+      <c r="JJ1" s="84"/>
+      <c r="JK1" s="84"/>
+      <c r="JL1" s="84"/>
+      <c r="JM1" s="84"/>
+      <c r="JN1" s="84"/>
+      <c r="JO1" s="84"/>
+      <c r="JP1" s="84"/>
+      <c r="JQ1" s="84"/>
+      <c r="JR1" s="84"/>
+      <c r="JS1" s="85"/>
+      <c r="JT1" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="JU1" s="83"/>
-      <c r="JV1" s="83"/>
-      <c r="JW1" s="83"/>
-      <c r="JX1" s="83"/>
-      <c r="JY1" s="83"/>
-      <c r="JZ1" s="83"/>
-      <c r="KA1" s="83"/>
-      <c r="KB1" s="83"/>
-      <c r="KC1" s="83"/>
-      <c r="KD1" s="83"/>
-      <c r="KE1" s="83"/>
-      <c r="KF1" s="83"/>
-      <c r="KG1" s="83"/>
-      <c r="KH1" s="83"/>
-      <c r="KI1" s="83"/>
-      <c r="KJ1" s="83"/>
-      <c r="KK1" s="83"/>
-      <c r="KL1" s="83"/>
-      <c r="KM1" s="83"/>
-      <c r="KN1" s="83"/>
-      <c r="KO1" s="83"/>
-      <c r="KP1" s="83"/>
-      <c r="KQ1" s="83"/>
-      <c r="KR1" s="83"/>
-      <c r="KS1" s="83"/>
-      <c r="KT1" s="83"/>
-      <c r="KU1" s="83"/>
+      <c r="JU1" s="84"/>
+      <c r="JV1" s="84"/>
+      <c r="JW1" s="84"/>
+      <c r="JX1" s="84"/>
+      <c r="JY1" s="84"/>
+      <c r="JZ1" s="84"/>
+      <c r="KA1" s="84"/>
+      <c r="KB1" s="84"/>
+      <c r="KC1" s="84"/>
+      <c r="KD1" s="84"/>
+      <c r="KE1" s="84"/>
+      <c r="KF1" s="84"/>
+      <c r="KG1" s="84"/>
+      <c r="KH1" s="84"/>
+      <c r="KI1" s="84"/>
+      <c r="KJ1" s="84"/>
+      <c r="KK1" s="84"/>
+      <c r="KL1" s="84"/>
+      <c r="KM1" s="84"/>
+      <c r="KN1" s="84"/>
+      <c r="KO1" s="84"/>
+      <c r="KP1" s="84"/>
+      <c r="KQ1" s="84"/>
+      <c r="KR1" s="84"/>
+      <c r="KS1" s="84"/>
+      <c r="KT1" s="84"/>
+      <c r="KU1" s="84"/>
     </row>
     <row r="2" spans="1:307" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -41191,8 +41191,12 @@
       <c r="C77" s="60"/>
       <c r="D77" s="60"/>
       <c r="E77" s="60"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="60"/>
+      <c r="F77" s="82">
+        <v>46296</v>
+      </c>
+      <c r="G77" s="82">
+        <v>46303</v>
+      </c>
       <c r="H77" s="61">
         <v>0</v>
       </c>
@@ -42066,8 +42070,12 @@
       <c r="C78" s="60"/>
       <c r="D78" s="60"/>
       <c r="E78" s="60"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="60"/>
+      <c r="F78" s="82">
+        <v>46296</v>
+      </c>
+      <c r="G78" s="82">
+        <v>46303</v>
+      </c>
       <c r="H78" s="61">
         <v>0</v>
       </c>
@@ -42941,8 +42949,12 @@
       <c r="C79" s="60"/>
       <c r="D79" s="60"/>
       <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
+      <c r="F79" s="82">
+        <v>46328</v>
+      </c>
+      <c r="G79" s="82">
+        <v>46349</v>
+      </c>
       <c r="H79" s="61">
         <v>0</v>
       </c>
@@ -43816,10 +43828,10 @@
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
       <c r="E80" s="60"/>
-      <c r="F80" s="86">
+      <c r="F80" s="82">
         <v>46351</v>
       </c>
-      <c r="G80" s="86">
+      <c r="G80" s="82">
         <v>46351</v>
       </c>
       <c r="H80" s="61">

--- a/docs/【Creepy Code】ガントチャート_PC.xlsx
+++ b/docs/【Creepy Code】ガントチャート_PC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nishi\OneDrive\ドキュメント\Creepy-Code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90880DD5-45E1-4584-B443-3529BD37AABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDA0DD2-1D85-4A22-8188-C0AB0E2FCB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="117">
   <si>
     <t>※作業予定（期間）を黄色く色づけする</t>
   </si>
@@ -557,6 +557,51 @@
     </r>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>2026/</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>基本機能の決定</t>
+    <rPh sb="0" eb="4">
+      <t>キホンキノウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>基本機能実装</t>
+    <rPh sb="0" eb="4">
+      <t>キホンキノウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>中間発表用スライド作成</t>
+    <rPh sb="0" eb="2">
+      <t>チュウカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッピョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>中間発表原稿作成</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>中間発表リハーサル</t>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
@@ -567,7 +612,7 @@
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="178" formatCode="m/d"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -716,6 +761,14 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="18">
@@ -960,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1106,6 +1159,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -24139,7 +24193,9 @@
       <c r="C53" s="37"/>
       <c r="D53" s="37"/>
       <c r="E53" s="37"/>
-      <c r="F53" s="38"/>
+      <c r="F53" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="G53" s="38"/>
       <c r="H53" s="39">
         <v>0</v>
@@ -25008,12 +25064,18 @@
       <c r="A54" s="35">
         <v>2</v>
       </c>
-      <c r="B54" s="37"/>
+      <c r="B54" s="87" t="s">
+        <v>112</v>
+      </c>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
       <c r="E54" s="37"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
+      <c r="F54" s="38">
+        <v>46266</v>
+      </c>
+      <c r="G54" s="38">
+        <v>46266</v>
+      </c>
       <c r="H54" s="39">
         <v>0</v>
       </c>
@@ -25881,12 +25943,18 @@
       <c r="A55" s="35">
         <v>3</v>
       </c>
-      <c r="B55" s="37"/>
+      <c r="B55" s="87" t="s">
+        <v>113</v>
+      </c>
       <c r="C55" s="37"/>
       <c r="D55" s="37"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
+      <c r="F55" s="38">
+        <v>46267</v>
+      </c>
+      <c r="G55" s="38">
+        <v>46310</v>
+      </c>
       <c r="H55" s="39">
         <v>0</v>
       </c>
@@ -41185,8 +41253,8 @@
       <c r="A77" s="58">
         <v>1</v>
       </c>
-      <c r="B77" s="59" t="s">
-        <v>70</v>
+      <c r="B77" s="62" t="s">
+        <v>114</v>
       </c>
       <c r="C77" s="60"/>
       <c r="D77" s="60"/>
@@ -42064,14 +42132,14 @@
       <c r="A78" s="58">
         <v>2</v>
       </c>
-      <c r="B78" s="59" t="s">
-        <v>71</v>
+      <c r="B78" s="62" t="s">
+        <v>115</v>
       </c>
       <c r="C78" s="60"/>
       <c r="D78" s="60"/>
       <c r="E78" s="60"/>
       <c r="F78" s="82">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="G78" s="82">
         <v>46303</v>
@@ -42943,8 +43011,8 @@
       <c r="A79" s="58">
         <v>3</v>
       </c>
-      <c r="B79" s="59" t="s">
-        <v>72</v>
+      <c r="B79" s="62" t="s">
+        <v>116</v>
       </c>
       <c r="C79" s="60"/>
       <c r="D79" s="60"/>
